--- a/kinds_Read_Origin.xlsx
+++ b/kinds_Read_Origin.xlsx
@@ -565,6 +565,8 @@
           <t>Danh sách nội dung — Read_Origin</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -589,7 +591,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>SKILL.md</t>
+          <t>SKILL</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -819,7 +821,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>KIND 120007_1 — Đoạn văn ngắn (Khó) [59~64] (Tách từ 120007)</t>
+          <t>KIND 120007_1 — Chèn câu vào đúng vị trí [59~60]</t>
         </is>
       </c>
     </row>
@@ -834,7 +836,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>KIND 120007_2 — Đoạn văn ngắn (Khó) [59~64] (Tách từ 120007)</t>
+          <t>KIND 120007_2 — Điền từ/cụm từ vào chỗ trống ㉠ [61~68]</t>
         </is>
       </c>
     </row>
@@ -849,7 +851,7 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>KIND 120007_3 — Đoạn văn ngắn (Khó) [59~64] (Tách từ 120007)</t>
+          <t>KIND 120007_3 — Đọc thông báo/poster (Ảnh) + 2 câu hỏi [69~70]</t>
         </is>
       </c>
     </row>
@@ -1214,6 +1216,11 @@
           <t>Kind: 120003_1</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -1221,6 +1228,11 @@
           <t>KIND 120003_1 — Chọn đáp án sai [40~42] (Tách từ 120003)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -1228,6 +1240,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -1307,6 +1324,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -1482,6 +1504,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -1496,6 +1523,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -1551,6 +1583,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -1643,6 +1680,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -1678,6 +1720,11 @@
           <t>Cách mô tả ảnh (q_image_description)</t>
         </is>
       </c>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -1692,6 +1739,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -1727,6 +1779,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -1769,6 +1826,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -1931,6 +1993,11 @@
           <t>Kind: 120003_2</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -1938,6 +2005,11 @@
           <t>KIND 120003_2 — Chọn đáp án sai [40~42] (Tách từ 120003)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -1945,6 +2017,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -2024,6 +2101,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -2195,6 +2277,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -2209,6 +2296,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -2264,6 +2356,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -2356,6 +2453,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -2391,6 +2493,11 @@
           <t>Cách mô tả ảnh (q_image_description)</t>
         </is>
       </c>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -2405,6 +2512,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -2440,6 +2552,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -2482,6 +2599,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -2644,6 +2766,11 @@
           <t>Kind: 120004_1</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -2651,6 +2778,11 @@
           <t>KIND 120004_1 — Nội dung khớp (TOPIK I, Level 1)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -2665,6 +2797,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -2768,6 +2905,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -2949,6 +3091,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -2963,6 +3110,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
@@ -3018,6 +3170,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
@@ -3110,6 +3267,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -3145,6 +3307,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
@@ -3173,6 +3340,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -3215,6 +3387,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B67" s="10" t="n"/>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="10" t="n"/>
+      <c r="E67" s="10" t="n"/>
+      <c r="F67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
@@ -3306,6 +3483,11 @@
           <t>Kind: 120004_2</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -3313,6 +3495,11 @@
           <t>KIND 120004_2 — Ý chính / Trung tâm (TOPIK I, Level 1)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -3327,6 +3514,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -3430,6 +3622,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -3611,6 +3808,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -3625,6 +3827,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
@@ -3680,6 +3887,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
@@ -3772,6 +3984,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -3807,6 +4024,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
@@ -3835,6 +4057,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -3877,6 +4104,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B67" s="10" t="n"/>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="10" t="n"/>
+      <c r="E67" s="10" t="n"/>
+      <c r="F67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
@@ -3968,6 +4200,11 @@
           <t>Kind: 120005</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -3975,6 +4212,11 @@
           <t>KIND 120005 — Đọc đoạn + 2 câu hỏi (TOPIK I, Level 1)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -3982,6 +4224,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -4085,6 +4332,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -4292,6 +4544,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -4306,6 +4563,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
@@ -4361,6 +4623,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="13" t="inlineStr">
@@ -4484,6 +4751,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
@@ -4519,6 +4791,11 @@
           <t>Cấu trúc đáp án — 2 câu hỏi con</t>
         </is>
       </c>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="10" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="13" t="inlineStr">
@@ -4582,6 +4859,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B71" s="10" t="n"/>
+      <c r="C71" s="10" t="n"/>
+      <c r="D71" s="10" t="n"/>
+      <c r="E71" s="10" t="n"/>
+      <c r="F71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
@@ -4624,6 +4906,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B77" s="10" t="n"/>
+      <c r="C77" s="10" t="n"/>
+      <c r="D77" s="10" t="n"/>
+      <c r="E77" s="10" t="n"/>
+      <c r="F77" s="10" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
@@ -4852,6 +5139,11 @@
           <t>Kind: 120006</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -4859,6 +5151,11 @@
           <t>KIND 120006 — Sắp xếp câu theo thứ tự (TOPIK I, Level 1)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -4866,6 +5163,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -4969,6 +5271,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -5144,6 +5451,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -5158,6 +5470,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -5213,6 +5530,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -5254,6 +5576,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -5289,6 +5616,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -5324,6 +5656,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -5373,6 +5710,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B59" s="10" t="n"/>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
@@ -5486,6 +5828,11 @@
           <t>Kind: 120007</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -5493,6 +5840,11 @@
           <t>KIND 120007 — DEPRECATED</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -5517,7 +5869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5534,13 +5886,23 @@
           <t>Kind: 120007_1</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>KIND 120007_1 — Đoạn văn ngắn (Khó) [59~64] (Tách từ 120007)</t>
-        </is>
-      </c>
+          <t>KIND 120007_1 — Chèn câu vào đúng vị trí [59~60]</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -5548,6 +5910,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -5605,7 +5972,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Đoạn văn ngắn (Khó) [59~64]</t>
+          <t>Chèn câu vào đúng vị trí [59~60]</t>
         </is>
       </c>
     </row>
@@ -5617,7 +5984,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Short paragraph (Difficult) [59~64]</t>
+          <t>Insert sentence at correct position [59~60]</t>
         </is>
       </c>
     </row>
@@ -5627,6 +5994,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -5672,7 +6044,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Đọc đoạn văn và chọn đáp án đúng (khó). (Ấn vào ảnh để phóng to).</t>
+          <t>Đọc đoạn văn và chọn vị trí đúng để chèn câu.</t>
         </is>
       </c>
     </row>
@@ -5684,7 +6056,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Read the passage and choose the correct answer (difficult). (Click image to enlarge).</t>
+          <t>Read the passage and choose the correct position to insert the sentence.</t>
         </is>
       </c>
     </row>
@@ -5799,158 +6171,145 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Chủ đề thường gặp</t>
-        </is>
-      </c>
+          <t>Đặc điểm riêng — KHÁC với 120007_2 và 120007_3</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Đa dạng, nội dung phong phú hơn 120005: 문화(văn hóa), 사회(xã hội), 건강(sức khỏe), 환경(môi trường), 교육(giáo dục), 여행(du lịch), 직장(công sở). Đoạn văn có chiều sâu hơn, thường bao gồm lý do, kết quả, ý kiến.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>Nhãn hệ thống</t>
+          <t>Dạng chèn câu (Sentence Insertion):</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>• Đoạn văn có 4 vị trí đánh dấu: ㉠ ㉡ ㉢ ㉣ xen giữa các câu</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>Nhãn</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>Giá trị</t>
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>• Câu hỏi 1 cho một câu và hỏi: câu đó nên đặt ở vị trí nào?</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>question_feature</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>`qf_multi_passage`</t>
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>• Đáp án là 4 ký hiệu vị trí: ㉠, ㉡, ㉢, ㉣</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>text_format</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>`text_passage_multi`</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>answer_grammar</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>content[0]: `ans_word_phrase` hoặc `ans_sentence_plain`, content[1]: `ans_sentence_plain`</t>
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>• KHÔNG phải điền từ — mà là chèn cả câu vào đúng chỗ</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Chủ đề thường gặp</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Đa dạng: 문화(văn hóa), 사회(xã hội), 건강(sức khỏe), 환경(môi trường), 교육(giáo dục), 여행(du lịch), 직장(công sở). Đoạn văn có chiều sâu, bao gồm lý do, kết quả, ý kiến.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Chiến lược bẫy</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
-        <is>
-          <t>content[0] — Điền chỗ trống ㉠ hoặc thái độ/ý định</t>
+          <t>Nhãn hệ thống</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>Nhãn</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Giá trị</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="inlineStr">
-        <is>
-          <t>Bẫy</t>
-        </is>
-      </c>
-      <c r="B38" s="14" t="inlineStr">
-        <is>
-          <t>Tỷ lệ</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>question_feature</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>`qf_sentence_insert`</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>`trap_synonym_swap`</t>
+          <t>text_format</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Từ gần nghĩa nhưng sai ngữ cảnh</t>
+          <t>`text_passage_multi`</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>`trap_shared_noun`</t>
+          <t>answer_grammar</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Dùng lại từ trong đoạn, sai nghĩa</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>`trap_wrong_inference`</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Suy luận hợp lý nhưng sai</t>
-        </is>
-      </c>
+          <t>content[0]: `ans_position_mark` (㉠/㉡/㉢/㉣), content[1]: `ans_sentence_plain`</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>Chiến lược bẫy</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>content[1] — Nội dung khớp</t>
+          <t>content[0] — Chèn câu vào vị trí</t>
         </is>
       </c>
     </row>
@@ -5974,397 +6333,482 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>`trap_partial_truth`</t>
+          <t>`trap_order_swap`</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Nửa đúng nửa sai</t>
+          <t>Vị trí gần đúng nhưng lệch 1 bước — câu hợp lý ở vị trí kế bên</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>`trap_detail_distort`</t>
+          <t>`trap_partial_truth`</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Thay đổi chi tiết cụ thể</t>
+          <t>Vị trí nơi câu chèn khớp 1 phần ngữ cảnh nhưng phá vỡ logic tổng thể</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
+          <t>`trap_wrong_inference`</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Vị trí mà câu chèn có vẻ liên quan chủ đề nhưng không nối mạch ý</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>content[1] — Nội dung khớp</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>Bẫy</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>`trap_partial_truth`</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Nửa đúng nửa sai</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>`trap_detail_distort`</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Thay đổi chi tiết cụ thể</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
           <t>`trap_subject_swap`</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>Hoán đổi chủ ngữ</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>• g_text: đoạn văn dài (~170-260 ký tự, 5-8 câu)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>• Một số bài có ký hiệu ㉠ (chỗ trống), một số không</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>• Nội dung phong phú: mô tả, giải thích, kể chuyện, nêu quan điểm</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>• Dùng chung cho cả 2 câu hỏi</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>Cấu trúc đáp án — 2 câu hỏi con</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="13" t="inlineStr">
-        <is>
-          <t>content[0] (q_point = 2-3): Điền chỗ trống hoặc thái độ/ý định</t>
-        </is>
-      </c>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>• Dạng q_text:</t>
+          <t>• g_text: đoạn văn (~150-250 ký tự, 4-6 câu) với 4 ký hiệu vị trí ㉠ ㉡ ㉢ ㉣ xen giữa các câu</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>• "㉠에 들어갈 알맞은 말을 고르십시오." (nếu có ㉠)</t>
+          <t>• Các vị trí phải nằm ở đầu, giữa, hoặc cuối các câu — tạo 4 lựa chọn hợp lý</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>• "이 글을 쓴 목적을 고르십시오." (mục đích viết)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>• "이 사람의 기분을 고르십시오." (tâm trạng)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="11" t="inlineStr">
-        <is>
-          <t>• 4 đáp án phù hợp dạng câu hỏi</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="13" t="inlineStr">
-        <is>
-          <t>content[1] (q_point = 2-3): Nội dung khớp</t>
+          <t>• Đoạn văn phải có mạch logic rõ ràng: theo thời gian, nhân quả, hoặc luận điểm</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>Cấu trúc đáp án — 2 câu hỏi con (count_question = 2)</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="n"/>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="10" t="n"/>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>content[0] (q_point = 2-3): Chèn câu vào vị trí</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>• q_text chứa câu cần chèn + câu hỏi: "다음 문장이 들어갈 곳을 고르십시오."</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>• q_text: "이 글의 내용과 같은 것을 고르십시오."</t>
+          <t>• Hoặc dạng: "&lt;câu cần chèn&gt;\n위 문장이 들어갈 곳을 고르십시오."</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>• 4 câu trần thuật mô tả nội dung đoạn văn</t>
+          <t>• 4 đáp án: ["㉠", "㉡", "㉢", "㉣"]</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>• Đáp án đúng: câu khớp chính xác 1 thông tin trong đoạn</t>
+          <t>• Đáp án đúng: vị trí mà câu chèn nối mạch ý tốt nhất</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="9" t="inlineStr">
-        <is>
-          <t>Quy tắc bắt buộc</t>
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>content[1] (q_point = 2-3): Nội dung khớp</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>1. g_text PHẢI đủ dài (~170-260 ký tự) và chứa đủ thông tin cho 2 câu hỏi</t>
+          <t>• q_text: "이 글의 내용과 같은 것을 고르십시오."</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>2. Nếu có ㉠, chỉ được có 1 chỗ trống</t>
+          <t>• 4 câu trần thuật mô tả nội dung đoạn văn</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>3. content[0] và content[1] PHẢI hỏi về khía cạnh khác nhau của đoạn văn</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t>4. Độ khó cao hơn 120005: đoạn dài hơn, từ vựng phong phú hơn, bẫy tinh vi hơn</t>
-        </is>
-      </c>
+          <t>• Đáp án đúng: câu khớp chính xác 1 thông tin trong đoạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>Quy tắc bắt buộc</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="n"/>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="10" t="n"/>
+      <c r="F69" s="10" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>5. Sub-kind _1: đơn giản nhất; _2: trung bình, thường có ㉠; _3: khó nhất, đoạn dài nhất</t>
+          <t>1. g_text PHẢI có đúng 4 ký hiệu vị trí ㉠ ㉡ ㉢ ㉣ (không thừa, không thiếu)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>6. Ngữ pháp nâng cao hơn nhưng vẫn trong phạm vi TOPIK I (~(으)ㄹ 수 있다, ~(으)면, ~기 때문에)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="9" t="inlineStr">
+          <t>2. Câu cần chèn phải chỉ khớp logic ở 1 vị trí duy nhất — 3 vị trí còn lại phải sai rõ</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>3. Đoạn văn cần mạch logic chặt chẽ: chèn sai vị trí sẽ phá vỡ mạch ý</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>4. content[0] đáp án là ㉠/㉡/㉢/㉣ — KHÔNG phải từ/cụm từ</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>5. content[0] và content[1] PHẢI hỏi về khía cạnh khác nhau của đoạn văn</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>6. Ngữ pháp nâng cao nhưng trong phạm vi TOPIK I (~(으)ㄹ 수 있다, ~(으)면, ~기 때문에)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="9" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="12" t="inlineStr">
-        <is>
-          <t>{</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "g_text": "저는 작년에 한국에 왔습니다. 처음에는 한국어를 잘 몰라서 힘들었습니다. ㉠ 한국어 학원에 다니기 시작했습니다. 매일 열심히 공부했습니다. 지금은 한국 친구도 많이 사귀었고 한국 생활이 재미있습니다. 주말에는 친구들과 같이 맛있는 음식도 먹고 여행도 갑니다.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "content": [</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    {</t>
-        </is>
-      </c>
+      <c r="B76" s="10" t="n"/>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="10" t="n"/>
+      <c r="F76" s="10" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "q_text": "㉠에 들어갈 알맞은 말을 고르십시오.",</t>
+          <t>{</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "q_answer": ["그래서", "그러나", "그리고", "그러면"],</t>
+          <t xml:space="preserve">  "g_text": "요즘 사람들은 건강에 관심이 많습니다. ㉠ 그래서 운동을 하는 사람들이 많아졌습니다. ㉡ 특히 아침에 공원에서 달리기를 하는 사람들을 자주 볼 수 있습니다. ㉢ 운동을 하면 몸도 건강해지고 기분도 좋아집니다. ㉣",</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "q_correct": 1</t>
+          <t xml:space="preserve">  "content": [</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    },</t>
+          <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    {</t>
+          <t xml:space="preserve">      "q_text": "건강을 위해서 음식도 중요하지만 운동이 더 중요합니다.\n위 문장이 들어갈 곳을 고르십시오.",</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "q_text": "이 글의 내용과 같은 것을 고르십시오.",</t>
+          <t xml:space="preserve">      "q_answer": ["㉠", "㉡", "㉢", "㉣"],</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "q_answer": [</t>
+          <t xml:space="preserve">      "q_correct": 1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "저는 올해 한국에 왔습니다.",</t>
+          <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "저는 한국어를 잘합니다.",</t>
+          <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "저는 주말에 혼자 여행을 갑니다.",</t>
+          <t xml:space="preserve">      "q_text": "이 글의 내용과 같은 것을 고르십시오.",</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "저는 지금 한국 생활이 즐겁습니다."</t>
+          <t xml:space="preserve">      "q_answer": [</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ],</t>
+          <t xml:space="preserve">        "요즘 사람들은 건강에 관심이 없습니다.",</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "q_correct": 4</t>
+          <t xml:space="preserve">        "운동을 하는 사람들이 줄어들었습니다.",</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    }</t>
+          <t xml:space="preserve">        "아침에 공원에서 달리기를 하는 사람들이 있습니다.",</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ]</t>
+          <t xml:space="preserve">        "운동을 하면 기분이 나빠집니다."</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">      ],</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      "q_correct": 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    }</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
           <t>}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="54">
-    <mergeCell ref="A54:F54"/>
+  <mergeCells count="58">
     <mergeCell ref="A84:F84"/>
     <mergeCell ref="A90:F90"/>
     <mergeCell ref="A66:F66"/>
     <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A75:F75"/>
     <mergeCell ref="A89:F89"/>
     <mergeCell ref="A74:F74"/>
     <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A50:F50"/>
     <mergeCell ref="A56:F56"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A86:F86"/>
     <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A95:F95"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A71:F71"/>
     <mergeCell ref="A85:F85"/>
+    <mergeCell ref="A42:F42"/>
     <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A62:F62"/>
-    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A96:F96"/>
+    <mergeCell ref="A91:F91"/>
     <mergeCell ref="A72:F72"/>
     <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A91:F91"/>
     <mergeCell ref="A43:F43"/>
     <mergeCell ref="A81:F81"/>
     <mergeCell ref="A63:F63"/>
-    <mergeCell ref="A52:F52"/>
     <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A93:F93"/>
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A83:F83"/>
     <mergeCell ref="A92:F92"/>
     <mergeCell ref="A30:F30"/>
@@ -6373,11 +6817,11 @@
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="A73:F73"/>
     <mergeCell ref="A49:F49"/>
-    <mergeCell ref="A51:F51"/>
     <mergeCell ref="A82:F82"/>
     <mergeCell ref="A60:F60"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A70:F70"/>
     <mergeCell ref="A79:F79"/>
     <mergeCell ref="A61:F61"/>
@@ -6397,7 +6841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6414,13 +6858,23 @@
           <t>Kind: 120007_2</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>KIND 120007_2 — Đoạn văn ngắn (Khó) [59~64] (Tách từ 120007)</t>
-        </is>
-      </c>
+          <t>KIND 120007_2 — Điền từ/cụm từ vào chỗ trống ㉠ [61~68]</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -6428,6 +6882,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -6485,7 +6944,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Đoạn văn ngắn (Khó) [59~64]</t>
+          <t>Điền từ/cụm từ vào chỗ trống [61~68]</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6956,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Short paragraph (Difficult) [59~64]</t>
+          <t>Fill in word/phrase [61~68]</t>
         </is>
       </c>
     </row>
@@ -6507,6 +6966,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -6552,7 +7016,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Đọc đoạn văn và chọn đáp án đúng (khó). (Ấn vào ảnh để phóng to).</t>
+          <t>Đọc đoạn văn và chọn từ/cụm từ phù hợp điền vào chỗ trống.</t>
         </is>
       </c>
     </row>
@@ -6564,7 +7028,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Read the passage and choose the correct answer (difficult). (Click image to enlarge).</t>
+          <t>Read the passage and choose the correct word/phrase for the blank.</t>
         </is>
       </c>
     </row>
@@ -6598,247 +7062,301 @@
           <t>Intro text</t>
         </is>
       </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>[61～62] 다음을 읽고 물음에 답하십시오.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Questions</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>[61～68]</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>[63～64] 다음을 읽고 물음에 답하십시오.</t>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Phân loại</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>0 (0=câu ghép, 1=câu đơn)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>[65～66] 다음을 읽고 물음에 답하십시오.</t>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Độ khó</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>[67～68] 다음을 읽고 물음에  |</t>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>2-2, 2-3, 3-3, 3-3</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>Questions</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>[61～68]</t>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Thời gian/câu (giây)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Phân loại</t>
+          <t>Số câu trong đề</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>0 (0=câu ghép, 1=câu đơn)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Độ khó</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Score</t>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Đặc điểm riêng — KHÁC với 120007_1 và 120007_3</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Dạng điền từ/cụm từ (Fill in Word/Phrase):</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>• Đoạn văn có 1 chỗ trống ㉠ duy nhất</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>3-3</t>
+          <t>• Câu hỏi 1: chọn từ/cụm từ phù hợp điền vào ㉠</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>3-3 |</t>
+          <t>• Đáp án là 4 từ hoặc cụm từ tiếng Hàn (liên từ: 그래서/하지만/그런데, hoặc cụm động từ)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>Thời gian/câu (giây)</t>
-        </is>
-      </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>200</t>
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>• KHÔNG có ảnh — bài đọc hoàn toàn là văn bản</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Số câu trong đề</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>• Đây là dạng nhiều câu nhất (82 câu, 4 cặp trong đề thi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>Đa dạng, nội dung phong phú hơn 120005: 문화(văn hóa), 사회(xã hội), 건강(sức khỏe), 환경(môi trường), 교육(giáo dục), 여행(du lịch), 직장(công sở). Đoạn văn có chiều sâu hơn, thường bao gồm lý do, kết quả, ý kiến.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>Đa dạng: 문화(văn hóa), 사회(xã hội), 건강(sức khỏe), 환경(môi trường), 교육(giáo dục), 여행(du lịch), 직장(công sở). Đoạn văn có chiều sâu, bao gồm lý do, kết quả, ý kiến.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>Nhãn</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Giá trị</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="inlineStr">
-        <is>
-          <t>Nhãn</t>
-        </is>
-      </c>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>Giá trị</t>
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>question_feature</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>`qf_fill_blank` + `qf_content_match`</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>question_feature</t>
+          <t>text_format</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>`qf_multi_passage`</t>
+          <t>`text_passage_multi`</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>text_format</t>
+          <t>answer_grammar</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>`text_passage_multi`</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>answer_grammar</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>content[0]: `ans_word_phrase` hoặc `ans_sentence_plain`, content[1]: `ans_sentence_plain`</t>
-        </is>
-      </c>
+          <t>content[0]: `ans_word_phrase` (từ/cụm từ ngắn), content[1]: `ans_sentence_plain`</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Chiến lược bẫy</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>Chiến lược bẫy</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="13" t="inlineStr">
-        <is>
-          <t>content[0] — Điền chỗ trống ㉠ hoặc thái độ/ý định</t>
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>content[0] — Điền từ/cụm từ vào ㉠</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>Bẫy</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="inlineStr">
-        <is>
-          <t>Bẫy</t>
-        </is>
-      </c>
-      <c r="B46" s="14" t="inlineStr">
-        <is>
-          <t>Tỷ lệ</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>`trap_synonym_swap`</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Từ gần nghĩa nhưng sai ngữ cảnh (e.g. 그래서 vs 그러면)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>`trap_synonym_swap`</t>
+          <t>`trap_shared_noun`</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Từ gần nghĩa nhưng sai ngữ cảnh</t>
+          <t>Dùng lại từ trong đoạn nhưng sai logic nối</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>`trap_shared_noun`</t>
+          <t>`trap_grammar_connector`</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Dùng lại từ trong đoạn, sai nghĩa</t>
+          <t>Liên từ sai quan hệ nhân quả/tương phản/bổ sung</t>
         </is>
       </c>
     </row>
@@ -6855,7 +7373,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Suy luận hợp lý nhưng sai</t>
+          <t>Từ hợp lý bề ngoài nhưng phá vỡ mạch ý</t>
         </is>
       </c>
     </row>
@@ -6934,316 +7452,360 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="9" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>`trap_neg_없안`</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Đảo nghĩa bằng 없다/안</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>• g_text: đoạn văn dài (~170-260 ký tự, 5-8 câu)</t>
-        </is>
-      </c>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>• Một số bài có ký hiệu ㉠ (chỗ trống), một số không</t>
+          <t>• g_text: đoạn văn (~170-260 ký tự, 5-8 câu) với 1 chỗ trống ㉠ duy nhất</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>• Nội dung phong phú: mô tả, giải thích, kể chuyện, nêu quan điểm</t>
+          <t>• ㉠ thường nằm ở đầu câu hoặc giữa câu, đóng vai trò liên từ hoặc cụm bổ nghĩa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
+          <t>• Nội dung đa dạng: mô tả, giải thích, kể chuyện, nêu quan điểm</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
           <t>• Dùng chung cho cả 2 câu hỏi</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="9" t="inlineStr">
-        <is>
-          <t>Cấu trúc đáp án — 2 câu hỏi con</t>
-        </is>
-      </c>
-    </row>
     <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="13" t="inlineStr">
-        <is>
-          <t>content[0] (q_point = 2-3): Điền chỗ trống hoặc thái độ/ý định</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t>• Dạng q_text:</t>
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>Cấu trúc đáp án — 2 câu hỏi con (count_question = 2)</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="10" t="n"/>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>content[0] (q_point = 2-3): Điền từ/cụm vào ㉠</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>• "㉠에 들어갈 알맞은 말을 고르십시오." (nếu có ㉠)</t>
+          <t>• q_text: "㉠에 들어갈 알맞은 말을 고르십시오."</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>• "이 글을 쓴 목적을 고르십시오." (mục đích viết)</t>
+          <t>• 4 đáp án là từ/cụm từ tiếng Hàn, thường thuộc các dạng:</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>• "이 사람의 기분을 고르십시오." (tâm trạng)</t>
+          <t>• Liên từ: 그래서, 하지만, 그런데, 그러면, 그리고, 그러나</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>• 4 đáp án phù hợp dạng câu hỏi</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="13" t="inlineStr">
-        <is>
-          <t>content[1] (q_point = 2-3): Nội dung khớp</t>
+          <t>• Cụm động từ: 오래 쓰지, 자주 만나지, 많이 먹지</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>• Cụm bổ nghĩa: ngắn, cùng cấu trúc ngữ pháp</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>• q_text: "이 글의 내용과 같은 것을 고르십시오."</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t>• 4 câu trần thuật mô tả nội dung đoạn văn</t>
+          <t>• Đáp án đúng: từ/cụm duy nhất khớp logic + ngữ pháp tại vị trí ㉠</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>content[1] (q_point = 2-3): Nội dung khớp</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>• Đáp án đúng: câu khớp chính xác 1 thông tin trong đoạn</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="9" t="inlineStr">
-        <is>
-          <t>Quy tắc bắt buộc</t>
+          <t>• q_text: "이 글의 내용과 같은 것을 고르십시오."</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>• 4 câu trần thuật mô tả nội dung đoạn văn</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>1. g_text PHẢI đủ dài (~170-260 ký tự) và chứa đủ thông tin cho 2 câu hỏi</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>2. Nếu có ㉠, chỉ được có 1 chỗ trống</t>
-        </is>
-      </c>
+          <t>• Đáp án đúng: câu khớp chính xác 1 thông tin trong đoạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>Quy tắc bắt buộc</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="n"/>
+      <c r="C75" s="10" t="n"/>
+      <c r="D75" s="10" t="n"/>
+      <c r="E75" s="10" t="n"/>
+      <c r="F75" s="10" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>3. content[0] và content[1] PHẢI hỏi về khía cạnh khác nhau của đoạn văn</t>
+          <t>1. g_text PHẢI có đúng 1 chỗ trống ㉠ (không có ㉡ ㉢ ㉣)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>4. Độ khó cao hơn 120005: đoạn dài hơn, từ vựng phong phú hơn, bẫy tinh vi hơn</t>
+          <t>2. ㉠ phải ở vị trí mà chỉ 1 đáp án hợp logic — 3 đáp án còn lại SAI nhưng hấp dẫn</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>5. Sub-kind _1: đơn giản nhất; _2: trung bình, thường có ㉠; _3: khó nhất, đoạn dài nhất</t>
+          <t>3. 4 đáp án content[0] phải cùng loại (đều là liên từ, hoặc đều là cụm động từ, hoặc đều là cụm bổ nghĩa)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>6. Ngữ pháp nâng cao hơn nhưng vẫn trong phạm vi TOPIK I (~(으)ㄹ 수 있다, ~(으)면, ~기 때문에)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="9" t="inlineStr">
+          <t>4. content[0] và content[1] PHẢI hỏi về khía cạnh khác nhau</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>5. Đoạn văn phải đủ dài để content[1] có thông tin riêng (không chỉ lặp ý content[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>6. Ngữ pháp nâng cao nhưng trong phạm vi TOPIK I (~(으)ㄹ 수 있다, ~(으)면, ~기 때문에)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="9" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="12" t="inlineStr">
-        <is>
-          <t>{</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "g_text": "저는 작년에 한국에 왔습니다. 처음에는 한국어를 잘 몰라서 힘들었습니다. ㉠ 한국어 학원에 다니기 시작했습니다. 매일 열심히 공부했습니다. 지금은 한국 친구도 많이 사귀었고 한국 생활이 재미있습니다. 주말에는 친구들과 같이 맛있는 음식도 먹고 여행도 갑니다.",</t>
-        </is>
-      </c>
+      <c r="B82" s="10" t="n"/>
+      <c r="C82" s="10" t="n"/>
+      <c r="D82" s="10" t="n"/>
+      <c r="E82" s="10" t="n"/>
+      <c r="F82" s="10" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "content": [</t>
+          <t>{</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    {</t>
+          <t xml:space="preserve">  "g_text": "저는 작년에 한국에 왔습니다. 처음에는 한국어를 잘 몰라서 힘들었습니다. ㉠ 한국어 학원에 다니기 시작했습니다. 매일 열심히 공부했습니다. 지금은 한국 친구도 많이 사귀었고 한국 생활이 재미있습니다. 주말에는 친구들과 같이 맛있는 음식도 먹고 여행도 갑니다.",</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "q_text": "㉠에 들어갈 알맞은 말을 고르십시오.",</t>
+          <t xml:space="preserve">  "content": [</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "q_answer": ["그래서", "그러나", "그리고", "그러면"],</t>
+          <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "q_correct": 1</t>
+          <t xml:space="preserve">      "q_text": "㉠에 들어갈 알맞은 말을 고르십시오.",</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    },</t>
+          <t xml:space="preserve">      "q_answer": ["그래서", "그러나", "그리고", "그러면"],</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    {</t>
+          <t xml:space="preserve">      "q_correct": 1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "q_text": "이 글의 내용과 같은 것을 고르십시오.",</t>
+          <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "q_answer": [</t>
+          <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "저는 올해 한국에 왔습니다.",</t>
+          <t xml:space="preserve">      "q_text": "이 글의 내용과 같은 것을 고르십시오.",</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "저는 한국어를 잘합니다.",</t>
+          <t xml:space="preserve">      "q_answer": [</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "저는 주말에 혼자 여행을 갑니다.",</t>
+          <t xml:space="preserve">        "저는 올해 한국에 왔습니다.",</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "저는 지금 한국 생활이 즐겁습니다."</t>
+          <t xml:space="preserve">        "저는 한국어를 잘합니다.",</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ],</t>
+          <t xml:space="preserve">        "저는 주말에 혼자 여행을 갑니다.",</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "q_correct": 4</t>
+          <t xml:space="preserve">        "저는 지금 한국 생활이 즐겁습니다."</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    }</t>
+          <t xml:space="preserve">      ],</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ]</t>
+          <t xml:space="preserve">      "q_correct": 4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">    }</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="12" t="inlineStr">
+        <is>
           <t>}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="60">
+  <mergeCells count="62">
     <mergeCell ref="A99:F99"/>
     <mergeCell ref="A84:F84"/>
     <mergeCell ref="A90:F90"/>
@@ -7255,38 +7817,41 @@
     <mergeCell ref="A74:F74"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A101:F101"/>
     <mergeCell ref="A86:F86"/>
-    <mergeCell ref="A57:F57"/>
     <mergeCell ref="A95:F95"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A71:F71"/>
     <mergeCell ref="A85:F85"/>
     <mergeCell ref="A76:F76"/>
-    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A62:F62"/>
     <mergeCell ref="A100:F100"/>
     <mergeCell ref="A96:F96"/>
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="A72:F72"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A43:F43"/>
     <mergeCell ref="A81:F81"/>
-    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A93:F93"/>
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A102:F102"/>
     <mergeCell ref="A67:F67"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A83:F83"/>
     <mergeCell ref="A92:F92"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A77:F77"/>
     <mergeCell ref="A64:F64"/>
     <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A73:F73"/>
     <mergeCell ref="A51:F51"/>
     <mergeCell ref="A82:F82"/>
@@ -7294,10 +7859,9 @@
     <mergeCell ref="A98:F98"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A70:F70"/>
     <mergeCell ref="A79:F79"/>
-    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A61:F61"/>
     <mergeCell ref="A88:F88"/>
     <mergeCell ref="A78:F78"/>
@@ -7315,7 +7879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7332,13 +7896,23 @@
           <t>Kind: 120007_3</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>KIND 120007_3 — Đoạn văn ngắn (Khó) [59~64] (Tách từ 120007)</t>
-        </is>
-      </c>
+          <t>KIND 120007_3 — Đọc thông báo/poster (Ảnh) + 2 câu hỏi [69~70]</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -7346,6 +7920,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -7403,7 +7982,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Đoạn văn ngắn (Khó) [59~64]</t>
+          <t>Đọc thông báo/poster + 2 câu hỏi [69~70]</t>
         </is>
       </c>
     </row>
@@ -7415,7 +7994,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Short paragraph (Difficult) [59~64]</t>
+          <t>Read notice/poster (Image) + 2 questions [69~70]</t>
         </is>
       </c>
     </row>
@@ -7425,6 +8004,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -7470,7 +8054,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Đọc đoạn văn và chọn đáp án đúng (khó). (Ấn vào ảnh để phóng to).</t>
+          <t>Đọc thông báo/poster dạng ảnh và trả lời câu hỏi. (Ấn vào ảnh để phóng to).</t>
         </is>
       </c>
     </row>
@@ -7482,7 +8066,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Read the passage and choose the correct answer (difficult). (Click image to enlarge).</t>
+          <t>Read the notice/poster image and answer the questions. (Click image to enlarge).</t>
         </is>
       </c>
     </row>
@@ -7597,593 +8181,864 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Chủ đề thường gặp</t>
-        </is>
-      </c>
+          <t>Đặc điểm riêng — KHÁC với 120007_1 và 120007_2</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Đa dạng, nội dung phong phú hơn 120005: 문화(văn hóa), 사회(xã hội), 건강(sức khỏe), 환경(môi trường), 교육(giáo dục), 여행(du lịch), 직장(công sở). Đoạn văn có chiều sâu hơn, thường bao gồm lý do, kết quả, ý kiến.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+          <t>Dạng đọc ảnh (Image-based Reading):</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>• Bài đọc là ảnh (g_image) — thông báo, poster, quảng cáo, thư mời</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>• g_text rỗng — nội dung tiếng Hàn nằm trong ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>• g_text_translate chứa bản dịch vi/en của nội dung ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>• Câu hỏi 1: mục đích viết (왜 이 글을 썼습니까?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>• KHÔNG có chỗ trống ㉠ — hoàn toàn khác dạng điền</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Chủ đề thường gặp</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>Chủ đề thực tế đời sống: 모집(tuyển dụng), 행사 안내(thông báo sự kiện), 할인 안내(khuyến mãi), 동아리(câu lạc bộ), 수업 안내(thông báo lớp học), 이사(chuyển nhà), 초대(mời). Nội dung poster thường có: tiêu đề, thời gian, địa điểm, điều kiện, liên hệ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Nhãn hệ thống</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>Nhãn</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>Giá trị</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>question_feature</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>`qf_multi_passage`</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>text_format</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>`text_passage_multi`</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>answer_grammar</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>content[0]: `ans_word_phrase` hoặc `ans_sentence_plain`, content[1]: `ans_sentence_plain`</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>Chiến lược bẫy</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
-        <is>
-          <t>content[0] — Điền chỗ trống ㉠ hoặc thái độ/ý định</t>
-        </is>
-      </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Bẫy</t>
+          <t>Nhãn</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>Tỷ lệ</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
+          <t>Giá trị</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>`trap_synonym_swap`</t>
+          <t>question_feature</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Từ gần nghĩa nhưng sai ngữ cảnh</t>
+          <t>`qf_purpose_identify` + `qf_content_match`</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>`trap_shared_noun`</t>
+          <t>text_format</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Dùng lại từ trong đoạn, sai nghĩa</t>
+          <t>`text_notice_poster`</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>`trap_wrong_inference`</t>
+          <t>answer_grammar</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Suy luận hợp lý nhưng sai</t>
+          <t>content[0]: `ans_sentence_purpose` (câu mô tả mục đích ~(으)려고), content[1]: `ans_sentence_plain`</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="13" t="inlineStr">
-        <is>
-          <t>content[1] — Nội dung khớp</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="14" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Chiến lược bẫy</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>content[0] — Mục đích viết</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>Bẫy</t>
         </is>
       </c>
-      <c r="B44" s="14" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>Tỷ lệ</t>
         </is>
       </c>
-      <c r="C44" s="14" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>Mô tả</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>`trap_partial_truth`</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Nửa đúng nửa sai</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>`trap_detail_distort`</t>
+          <t>`trap_partial_truth`</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Thay đổi chi tiết cụ thể</t>
+          <t>Đáp án sai chứa thông tin có trong poster nhưng không phải mục đích chính</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
+          <t>`trap_detail_distort`</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Thay đổi chi tiết (e.g. "mời tham gia" → "thông báo hủy")</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>`trap_wrong_inference`</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Suy luận hợp lý từ poster nhưng sai mục đích</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
           <t>`trap_subject_swap`</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Hoán đổi chủ ngữ</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Gán hành động cho sai đối tượng</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>content[1] — Nội dung khớp</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>Bẫy</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>`trap_number_shift`</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Thay đổi ngày/giờ/số từ poster (e.g. 토요일→일요일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>`trap_detail_distort`</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Sai chi tiết địa điểm, điều kiện, giá</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>`trap_partial_truth`</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Nửa đúng nửa sai</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>`trap_subject_swap`</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Hoán đổi đối tượng</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>• g_text: đoạn văn dài (~170-260 ký tự, 5-8 câu)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>• Một số bài có ký hiệu ㉠ (chỗ trống), một số không</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>• Nội dung phong phú: mô tả, giải thích, kể chuyện, nêu quan điểm</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>• Dùng chung cho cả 2 câu hỏi</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>Cấu trúc đáp án — 2 câu hỏi con</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="13" t="inlineStr">
-        <is>
-          <t>content[0] (q_point = 2-3): Điền chỗ trống hoặc thái độ/ý định</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>• Dạng q_text:</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>• "㉠에 들어갈 알맞은 말을 고르십시오." (nếu có ㉠)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>• "이 글을 쓴 목적을 고르십시오." (mục đích viết)</t>
-        </is>
-      </c>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>• "이 사람의 기분을 고르십시오." (tâm trạng)</t>
+          <t>• g_text: rỗng ""</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>• 4 đáp án phù hợp dạng câu hỏi</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="13" t="inlineStr">
-        <is>
-          <t>content[1] (q_point = 2-3): Nội dung khớp</t>
+          <t>• g_image: URL ảnh thông báo/poster/quảng cáo</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>• g_text_translate: bản dịch vi/en mô tả nội dung ảnh</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>• q_text: "이 글의 내용과 같은 것을 고르십시오."</t>
+          <t>• g_image_description (hoặc q_image_description): mô tả chi tiết nội dung ảnh bằng text</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>• 4 câu trần thuật mô tả nội dung đoạn văn</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t>• Đáp án đúng: câu khớp chính xác 1 thông tin trong đoạn</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="9" t="inlineStr">
-        <is>
-          <t>Quy tắc bắt buộc</t>
+          <t>• Nội dung poster thường chứa: tiêu đề, nội dung chính, thời gian, địa điểm, đối tượng, điều kiện, số liên hệ</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>Format bổ sung — Mô tả ảnh</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="10" t="n"/>
+      <c r="F64" s="10" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>Vì bài đọc là ảnh, PHẢI có g_image_description mô tả chi tiết nội dung:</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>1. g_text PHẢI đủ dài (~170-260 ký tự) và chứa đủ thông tin cho 2 câu hỏi</t>
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>{</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t>2. Nếu có ㉠, chỉ được có 1 chỗ trống</t>
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  "g_image_description": {</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t>3. content[0] và content[1] PHẢI hỏi về khía cạnh khác nhau của đoạn văn</t>
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "image": "Poster thông báo tuyển thành viên câu lạc bộ nấu ăn. Tiêu đề: 요리 동아리 회원 모집. Nội dung: Thời gian hoạt động mỗi thứ 7, 10시~12시. Địa điểm: 학생 식당 2층. Đối tượng: 요리에 관심 있는 학생. Liên hệ: 김미영 010-1234-5678."</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t>4. Độ khó cao hơn 120005: đoạn dài hơn, từ vựng phong phú hơn, bẫy tinh vi hơn</t>
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  }</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t>5. Sub-kind _1: đơn giản nhất; _2: trung bình, thường có ㉠; _3: khó nhất, đoạn dài nhất</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t>6. Ngữ pháp nâng cao hơn nhưng vẫn trong phạm vi TOPIK I (~(으)ㄹ 수 있다, ~(으)면, ~기 때문에)</t>
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>}</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
+          <t>Cấu trúc đáp án — 2 câu hỏi con (count_question = 2)</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="n"/>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="10" t="n"/>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>content[0] (q_point = 2-3): Mục đích viết</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>• q_text dạng: "유미 씨는 왜 이 글을 썼습니까?" hoặc "이 글을 쓴 목적은 무엇입니까?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>• Tên người viết thường xuất hiện trong poster</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>• 4 đáp án: câu mô tả mục đích (~(으)려고, ~기 위해서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>• Đáp án đúng: mục đích chính của poster/thông báo</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>content[1] (q_point = 2-3): Nội dung khớp</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>• q_text: "이 글의 내용과 같은 것을 고르십시오."</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>• 4 câu trần thuật mô tả chi tiết từ poster</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>• Đáp án đúng: câu khớp chính xác 1 thông tin trong poster (ngày, giờ, địa điểm, điều kiện)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>Quy tắc bắt buộc</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="n"/>
+      <c r="C82" s="10" t="n"/>
+      <c r="D82" s="10" t="n"/>
+      <c r="E82" s="10" t="n"/>
+      <c r="F82" s="10" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>1. g_text PHẢI rỗng "" — nội dung nằm trong ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>2. PHẢI có g_image_description mô tả chi tiết poster (tiêu đề, thời gian, địa điểm, đối tượng, liên hệ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>3. Poster phải chứa đủ chi tiết (ít nhất 4 thông tin cụ thể) để content[1] có đủ bẫy</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="11" t="inlineStr">
+        <is>
+          <t>4. content[0] hỏi mục đích — KHÔNG phải điền từ hay chèn câu</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t>5. Tên người viết trong q_text phải khớp với tên liên hệ trong poster</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t>6. Bẫy content[1] phải thay đổi chi tiết cụ thể từ poster (ngày, giờ, địa điểm, số tiền)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t>7. Ngữ pháp phù hợp TOPIK I nhưng nội dung thực tế (thông báo, quảng cáo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
           <t>Ví dụ</t>
         </is>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="12" t="inlineStr">
-        <is>
-          <t>{</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "g_text": "저는 작년에 한국에 왔습니다. 처음에는 한국어를 잘 몰라서 힘들었습니다. ㉠ 한국어 학원에 다니기 시작했습니다. 매일 열심히 공부했습니다. 지금은 한국 친구도 많이 사귀었고 한국 생활이 재미있습니다. 주말에는 친구들과 같이 맛있는 음식도 먹고 여행도 갑니다.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "content": [</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    {</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      "q_text": "㉠에 들어갈 알맞은 말을 고르십시오.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      "q_answer": ["그래서", "그러나", "그리고", "그러면"],</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      "q_correct": 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    },</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    {</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      "q_text": "이 글의 내용과 같은 것을 고르십시오.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      "q_answer": [</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        "저는 올해 한국에 왔습니다.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        "저는 한국어를 잘합니다.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        "저는 주말에 혼자 여행을 갑니다.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        "저는 지금 한국 생활이 즐겁습니다."</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      ],</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      "q_correct": 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    }</t>
-        </is>
-      </c>
+      <c r="B90" s="10" t="n"/>
+      <c r="C90" s="10" t="n"/>
+      <c r="D90" s="10" t="n"/>
+      <c r="E90" s="10" t="n"/>
+      <c r="F90" s="10" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ]</t>
+          <t>{</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">  "g_text": "",</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  "g_image": "/topiks/images/example_poster.png",</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  "g_image_description": {</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "image": "Poster thông báo lớp học nấu ăn Hàn Quốc. Tiêu đề: 한국 요리 교실 안내. Thời gian: 매주 토요일 오후 2시~4시. Địa điểm: 문화센터 3층. Học phí: 50,000원 (재료비 포함). Đối tượng: 외국인 누구나. Liên hệ: 박지은 (010-9876-5432). Bắt đầu: 3월 5일부터."</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  },</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  "content": [</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    {</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      "q_text": "박지은 씨는 왜 이 글을 썼습니까?",</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      "q_answer": [</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "요리 교실에 사람들을 초대하려고",</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "한국 음식점을 소개하려고",</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "요리 대회 결과를 알려 주려고",</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "문화센터 위치를 안내하려고"</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      ],</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      "q_correct": 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    },</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    {</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      "q_text": "이 글의 내용과 같은 것을 고르십시오.",</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      "q_answer": [</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "수업은 일요일에 합니다.",</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "재료비는 따로 내야 합니다.",</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "한국 사람만 신청할 수 있습니다.",</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "수업은 문화센터에서 합니다."</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      ],</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      "q_correct": 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    }</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
           <t>}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="54">
-    <mergeCell ref="A54:F54"/>
+  <mergeCells count="78">
     <mergeCell ref="A84:F84"/>
-    <mergeCell ref="A90:F90"/>
     <mergeCell ref="A66:F66"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A118:F118"/>
     <mergeCell ref="A75:F75"/>
-    <mergeCell ref="A89:F89"/>
-    <mergeCell ref="A74:F74"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="A56:F56"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A55:F55"/>
     <mergeCell ref="A86:F86"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A85:F85"/>
-    <mergeCell ref="A76:F76"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A95:F95"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A97:F97"/>
     <mergeCell ref="A72:F72"/>
     <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A43:F43"/>
     <mergeCell ref="A81:F81"/>
-    <mergeCell ref="A63:F63"/>
-    <mergeCell ref="A52:F52"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A83:F83"/>
-    <mergeCell ref="A92:F92"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A77:F77"/>
     <mergeCell ref="A64:F64"/>
-    <mergeCell ref="A59:F59"/>
     <mergeCell ref="A73:F73"/>
-    <mergeCell ref="A49:F49"/>
     <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A107:F107"/>
     <mergeCell ref="A82:F82"/>
     <mergeCell ref="A60:F60"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A108:F108"/>
+    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A85:F85"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A112:F112"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A114:F114"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A98:F98"/>
     <mergeCell ref="A79:F79"/>
     <mergeCell ref="A61:F61"/>
     <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="A105:F105"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A116:F116"/>
+    <mergeCell ref="A100:F100"/>
+    <mergeCell ref="A109:F109"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="A93:F93"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A117:F117"/>
+    <mergeCell ref="A111:F111"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="A103:F103"/>
     <mergeCell ref="A78:F78"/>
-    <mergeCell ref="A69:F69"/>
     <mergeCell ref="A87:F87"/>
     <mergeCell ref="A65:F65"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A104:F104"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A106:F106"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A96:F96"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A110:F110"/>
+    <mergeCell ref="A119:F119"/>
+    <mergeCell ref="A69:F69"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8209,9 +9064,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>SKILL.md — Read_Origin</t>
-        </is>
-      </c>
+          <t>SKILL — Read_Origin</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -8219,6 +9079,11 @@
           <t>TOPIK Reading Question Generator (TOPIK I &amp; II)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -8233,6 +9098,11 @@
           <t>Khi nào dùng skill này</t>
         </is>
       </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -8261,6 +9131,11 @@
           <t>Cấu trúc thư mục</t>
         </is>
       </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -8548,6 +9423,11 @@
           <t>Output Format (JSON)</t>
         </is>
       </c>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -8993,6 +9873,11 @@
           <t>Danh mục chủ đề (topic)</t>
         </is>
       </c>
+      <c r="B109" s="10" t="n"/>
+      <c r="C109" s="10" t="n"/>
+      <c r="D109" s="10" t="n"/>
+      <c r="E109" s="10" t="n"/>
+      <c r="F109" s="10" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
@@ -9351,6 +10236,11 @@
           <t>Chiến lược bẫy đáp án sai (distractor_trap)</t>
         </is>
       </c>
+      <c r="B129" s="10" t="n"/>
+      <c r="C129" s="10" t="n"/>
+      <c r="D129" s="10" t="n"/>
+      <c r="E129" s="10" t="n"/>
+      <c r="F129" s="10" t="n"/>
     </row>
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="13" t="inlineStr">
@@ -9716,6 +10606,11 @@
           <t>Đặc điểm câu hỏi (question_feature)</t>
         </is>
       </c>
+      <c r="B158" s="10" t="n"/>
+      <c r="C158" s="10" t="n"/>
+      <c r="D158" s="10" t="n"/>
+      <c r="E158" s="10" t="n"/>
+      <c r="F158" s="10" t="n"/>
     </row>
     <row r="159" ht="22" customHeight="1">
       <c r="A159" s="13" t="inlineStr">
@@ -10001,6 +10896,11 @@
           <t>Định dạng văn bản đọc (text_format)</t>
         </is>
       </c>
+      <c r="B174" s="10" t="n"/>
+      <c r="C174" s="10" t="n"/>
+      <c r="D174" s="10" t="n"/>
+      <c r="E174" s="10" t="n"/>
+      <c r="F174" s="10" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
@@ -10198,6 +11098,11 @@
           <t>Ngữ pháp đáp án (answer_grammar)</t>
         </is>
       </c>
+      <c r="B186" s="10" t="n"/>
+      <c r="C186" s="10" t="n"/>
+      <c r="D186" s="10" t="n"/>
+      <c r="E186" s="10" t="n"/>
+      <c r="F186" s="10" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="14" t="inlineStr">
@@ -10348,6 +11253,11 @@
           <t>Thang độ khó (Difficulty Scale)</t>
         </is>
       </c>
+      <c r="B197" s="10" t="n"/>
+      <c r="C197" s="10" t="n"/>
+      <c r="D197" s="10" t="n"/>
+      <c r="E197" s="10" t="n"/>
+      <c r="F197" s="10" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="14" t="inlineStr">
@@ -10515,6 +11425,11 @@
           <t>Cấp độ đọc theo level (reading_level)</t>
         </is>
       </c>
+      <c r="B209" s="10" t="n"/>
+      <c r="C209" s="10" t="n"/>
+      <c r="D209" s="10" t="n"/>
+      <c r="E209" s="10" t="n"/>
+      <c r="F209" s="10" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="14" t="inlineStr">
@@ -10580,6 +11495,11 @@
           <t>Quy tắc chung khi gen câu hỏi</t>
         </is>
       </c>
+      <c r="B215" s="10" t="n"/>
+      <c r="C215" s="10" t="n"/>
+      <c r="D215" s="10" t="n"/>
+      <c r="E215" s="10" t="n"/>
+      <c r="F215" s="10" t="n"/>
     </row>
     <row r="216" ht="22" customHeight="1">
       <c r="A216" s="13" t="inlineStr">
@@ -10776,6 +11696,11 @@
           <t>Workflow</t>
         </is>
       </c>
+      <c r="B243" s="10" t="n"/>
+      <c r="C243" s="10" t="n"/>
+      <c r="D243" s="10" t="n"/>
+      <c r="E243" s="10" t="n"/>
+      <c r="F243" s="10" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="11" t="inlineStr">
@@ -11067,6 +11992,11 @@
           <t>Kind: 220001_a</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -11074,6 +12004,11 @@
           <t>KIND 220001_a — Điền ngữ pháp liên kết (TOPIK II, Level 2)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -11081,6 +12016,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -11184,6 +12124,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -11359,6 +12304,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -11373,6 +12323,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -11428,6 +12383,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -11486,6 +12446,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -11521,6 +12486,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -11549,6 +12519,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -11591,6 +12566,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
@@ -11702,6 +12682,11 @@
           <t>Kind: 220001_b</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -11709,6 +12694,11 @@
           <t>KIND 220001_b — Điền nội dung đoạn (TOPIK II, Level 2)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -11716,6 +12706,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -11819,6 +12814,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -11994,6 +12994,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -12008,6 +13013,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -12063,6 +13073,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -12155,6 +13170,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -12197,6 +13217,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -12225,6 +13250,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -12267,6 +13297,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -12379,6 +13414,11 @@
           <t>Kind: 220001_c</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -12386,6 +13426,11 @@
           <t>KIND 220001_c — Điền vào chỗ trống (Dễ) (3) [28~31]</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -12393,6 +13438,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -12484,6 +13534,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
@@ -12659,6 +13714,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
@@ -12673,6 +13733,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
@@ -12728,6 +13793,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
@@ -12820,6 +13890,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -12862,6 +13937,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -12890,6 +13970,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -12932,6 +14017,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
@@ -13044,6 +14134,11 @@
           <t>Kind: 220002_a</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -13051,6 +14146,11 @@
           <t>KIND 220002_a — Ý nghĩa tương tự (TOPIK II, Level 2)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -13058,6 +14158,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -13161,6 +14266,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -13336,6 +14446,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -13350,6 +14465,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -13405,6 +14525,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -13463,6 +14588,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -13498,6 +14628,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -13526,6 +14661,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -13568,6 +14708,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
@@ -13679,6 +14824,11 @@
           <t>Kind: 220002_b</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -13686,6 +14836,11 @@
           <t>KIND 220002_b — DEPRECATED</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -13727,6 +14882,11 @@
           <t>Kind: 220002_b_1</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -13734,6 +14894,11 @@
           <t>KIND 220002_b_1 — Nội dung tương tự (2) [9~12] (Tách từ 220002_b)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -13741,6 +14906,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -13820,6 +14990,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -13995,6 +15170,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -14009,6 +15189,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -14064,6 +15249,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -14156,6 +15346,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -14191,6 +15386,11 @@
           <t>Cách mô tả ảnh (q_image_description)</t>
         </is>
       </c>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -14205,6 +15405,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -14233,6 +15438,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -14275,6 +15485,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -14468,6 +15683,11 @@
           <t>Kind: 220002_b_2</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -14475,6 +15695,11 @@
           <t>KIND 220002_b_2 — Nội dung tương tự (2) [9~12] (Tách từ 220002_b)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -14482,6 +15707,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -14561,6 +15791,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -14732,6 +15967,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -14746,6 +15986,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -14801,6 +16046,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -14893,6 +16143,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -14928,6 +16183,11 @@
           <t>Cách mô tả ảnh (q_image_description)</t>
         </is>
       </c>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -14942,6 +16202,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -14970,6 +16235,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -15012,6 +16282,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -15205,6 +16480,11 @@
           <t>Kind: 220002_b_3</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -15212,6 +16492,11 @@
           <t>KIND 220002_b_3 — Nội dung tương tự (2) [9~12] (Tách từ 220002_b)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -15219,6 +16504,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -15298,6 +16588,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -15469,6 +16764,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -15483,6 +16783,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -15538,6 +16843,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -15630,6 +16940,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -15665,6 +16980,11 @@
           <t>Cách mô tả ảnh (q_image_description)</t>
         </is>
       </c>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -15679,6 +16999,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -15707,6 +17032,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -15749,6 +17079,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -15942,6 +17277,11 @@
           <t>Kind: 220002_c</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -15949,6 +17289,11 @@
           <t>KIND 220002_c — Nội dung khớp văn bản (TOPIK II, Level 2)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -15956,6 +17301,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -16059,6 +17409,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -16234,6 +17589,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -16248,6 +17608,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -16303,6 +17668,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -16419,6 +17789,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -16454,6 +17829,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -16482,6 +17862,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
@@ -16524,6 +17909,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="10" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
@@ -16636,6 +18026,11 @@
           <t>Kind: 220003_a</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -16643,6 +18038,11 @@
           <t>KIND 220003_a — DEPRECATED</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -16684,6 +18084,11 @@
           <t>Kind: 120001</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -16691,6 +18096,11 @@
           <t>KIND 120001 — Đoán chủ đề đoạn văn ngắn (TOPIK I, Level 1)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -16698,6 +18108,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -16801,6 +18216,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -16976,6 +18396,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -16990,6 +18415,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -17045,6 +18475,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -17103,6 +18538,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -17138,6 +18578,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -17166,6 +18611,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -17201,6 +18651,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
@@ -17295,6 +18750,11 @@
           <t>Kind: 220003_a_1</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -17302,6 +18762,11 @@
           <t>KIND 220003_a_1 — Chủ đề đoạn văn (1) [5~8] (Tách từ 220003_a)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -17309,6 +18774,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -17388,6 +18858,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -17563,6 +19038,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -17577,6 +19057,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -17632,6 +19117,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -17690,6 +19180,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -17725,6 +19220,11 @@
           <t>Cách mô tả ảnh (q_image_description)</t>
         </is>
       </c>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -17739,6 +19239,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -17767,6 +19272,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -17809,6 +19319,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -17962,6 +19477,11 @@
           <t>Kind: 220003_a_2</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -17969,6 +19489,11 @@
           <t>KIND 220003_a_2 — Chủ đề đoạn văn (1) [5~8] (Tách từ 220003_a)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -17976,6 +19501,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -18055,6 +19585,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -18226,6 +19761,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -18240,6 +19780,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -18295,6 +19840,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -18353,6 +19903,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -18388,6 +19943,11 @@
           <t>Cách mô tả ảnh (q_image_description)</t>
         </is>
       </c>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -18402,6 +19962,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -18430,6 +19995,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -18472,6 +20042,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -18625,6 +20200,11 @@
           <t>Kind: 220003_b</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -18632,6 +20212,11 @@
           <t>KIND 220003_b — Chủ đề đoạn văn dài (TOPIK II, Level 2)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -18639,6 +20224,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -18742,6 +20332,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -18917,6 +20512,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -18931,6 +20531,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -18986,6 +20591,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -19078,6 +20688,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -19120,6 +20735,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -19148,6 +20768,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -19190,6 +20815,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -19302,6 +20932,11 @@
           <t>Kind: 220004</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -19309,6 +20944,11 @@
           <t>KIND 220004 — Sắp xếp câu nâng cao (TOPIK II, Level 2)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -19316,6 +20956,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -19419,6 +21064,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -19594,6 +21244,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -19608,6 +21263,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -19663,6 +21323,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -19704,6 +21369,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -19746,6 +21416,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -19774,6 +21449,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -19816,6 +21496,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
@@ -19960,6 +21645,11 @@
           <t>Kind: 220005</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -19967,6 +21657,11 @@
           <t>KIND 220005 — DEPRECATED</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -20008,6 +21703,11 @@
           <t>Kind: 220005_1</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -20015,6 +21715,11 @@
           <t>KIND 220005_1 — Đoạn văn (Dễ) [19~24] (Tách từ 220005)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -20022,6 +21727,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -20101,6 +21811,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -20278,6 +21993,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -20292,6 +22012,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -20335,6 +22060,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
@@ -20410,6 +22140,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -20445,6 +22180,11 @@
           <t>Cấu trúc câu hỏi phụ</t>
         </is>
       </c>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -20473,6 +22213,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -20501,6 +22246,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
@@ -20543,6 +22293,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="10" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -20835,6 +22590,11 @@
           <t>Kind: 220005_2</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -20842,6 +22602,11 @@
           <t>KIND 220005_2 — Đoạn văn (Dễ) [19~24] (Tách từ 220005)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -20849,6 +22614,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -20928,6 +22698,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -21103,6 +22878,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -21117,6 +22897,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -21160,6 +22945,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -21235,6 +23025,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -21270,6 +23065,11 @@
           <t>Cấu trúc câu hỏi phụ</t>
         </is>
       </c>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -21298,6 +23098,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -21326,6 +23131,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -21368,6 +23178,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -21659,6 +23474,11 @@
           <t>Kind: 220006</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -21666,6 +23486,11 @@
           <t>KIND 220006 — Tiêu đề báo chí (TOPIK II, Level 2)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -21673,6 +23498,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -21776,6 +23606,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -21951,6 +23786,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -21965,6 +23805,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -22020,6 +23865,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -22095,6 +23945,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -22151,6 +24006,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -22179,6 +24039,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
@@ -22221,6 +24086,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="10" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
@@ -22335,6 +24205,11 @@
           <t>Kind: 220007</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -22342,6 +24217,11 @@
           <t>KIND 220007 — Chèn câu vào đúng vị trí (TOPIK II, Level 2)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -22349,6 +24229,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -22452,6 +24337,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -22627,6 +24517,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -22641,6 +24536,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -22696,6 +24596,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -22737,6 +24642,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -22772,6 +24682,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -22800,6 +24715,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -22842,6 +24762,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
@@ -22961,6 +24886,11 @@
           <t>Kind: 220008</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -22968,6 +24898,11 @@
           <t>KIND 220008 — DEPRECATED</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -23009,6 +24944,11 @@
           <t>Kind: 120002</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -23016,6 +24956,11 @@
           <t>KIND 120002 — DEPRECATED</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -23057,6 +25002,11 @@
           <t>Kind: 220008_1</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -23064,6 +25014,11 @@
           <t>KIND 220008_1 — Đoạn văn (Khó) [42~50] (Tách từ 220008)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -23071,6 +25026,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -23150,6 +25110,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -23334,6 +25299,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -23348,6 +25318,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
@@ -23391,6 +25366,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -23483,6 +25463,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -23539,6 +25524,11 @@
           <t>Cấu trúc câu hỏi phụ</t>
         </is>
       </c>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
@@ -23588,6 +25578,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
@@ -23637,6 +25632,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B67" s="10" t="n"/>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="10" t="n"/>
+      <c r="E67" s="10" t="n"/>
+      <c r="F67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
@@ -23686,6 +25686,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B74" s="10" t="n"/>
+      <c r="C74" s="10" t="n"/>
+      <c r="D74" s="10" t="n"/>
+      <c r="E74" s="10" t="n"/>
+      <c r="F74" s="10" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
@@ -23908,8 +25913,8 @@
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A101:F101"/>
     <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A86:F86"/>
     <mergeCell ref="A104:F104"/>
-    <mergeCell ref="A86:F86"/>
     <mergeCell ref="A57:F57"/>
     <mergeCell ref="A95:F95"/>
     <mergeCell ref="A33:F33"/>
@@ -23989,6 +25994,11 @@
           <t>Kind: 220008_2</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -23996,6 +26006,11 @@
           <t>KIND 220008_2 — Đoạn văn (Khó) [42~50] (Tách từ 220008)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -24003,6 +26018,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -24082,6 +26102,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -24257,6 +26282,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -24271,6 +26301,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -24314,6 +26349,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -24406,6 +26446,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -24462,6 +26507,11 @@
           <t>Cấu trúc câu hỏi phụ</t>
         </is>
       </c>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -24511,6 +26561,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
@@ -24560,6 +26615,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="10" t="n"/>
+      <c r="F64" s="10" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
@@ -24609,6 +26669,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B71" s="10" t="n"/>
+      <c r="C71" s="10" t="n"/>
+      <c r="D71" s="10" t="n"/>
+      <c r="E71" s="10" t="n"/>
+      <c r="F71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
@@ -24910,6 +26975,11 @@
           <t>Kind: 120002_1</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -24917,6 +26987,11 @@
           <t>KIND 120002_1 — Điền vào chỗ trống [34~39] (Tách từ 120002)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -24924,6 +26999,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -25003,6 +27083,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -25178,6 +27263,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -25220,6 +27310,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
@@ -25275,6 +27370,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
@@ -25350,6 +27450,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -25385,6 +27490,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -25413,6 +27523,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -25455,6 +27570,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -25554,6 +27674,11 @@
           <t>Kind: 120002_2</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -25561,6 +27686,11 @@
           <t>KIND 120002_2 — Điền vào chỗ trống [34~39] (Tách từ 120002)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -25568,6 +27698,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -25647,6 +27782,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -25818,6 +27958,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -25860,6 +28005,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
@@ -25915,6 +28065,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
@@ -25990,6 +28145,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -26025,6 +28185,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -26053,6 +28218,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -26095,6 +28265,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -26194,6 +28369,11 @@
           <t>Kind: 120002_3</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -26201,6 +28381,11 @@
           <t>KIND 120002_3 — Điền vào chỗ trống [34~39] (Tách từ 120002)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -26208,6 +28393,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -26287,6 +28477,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -26458,6 +28653,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -26500,6 +28700,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
@@ -26555,6 +28760,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
@@ -26630,6 +28840,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -26665,6 +28880,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -26693,6 +28913,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -26735,6 +28960,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -26834,6 +29064,11 @@
           <t>Kind: 120002_4</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -26841,6 +29076,11 @@
           <t>KIND 120002_4 — Điền vào chỗ trống [34~39] (Tách từ 120002)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -26848,6 +29088,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -26927,6 +29172,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -27098,6 +29348,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -27140,6 +29395,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
@@ -27195,6 +29455,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
@@ -27270,6 +29535,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -27305,6 +29575,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -27333,6 +29608,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -27375,6 +29655,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -27474,6 +29759,11 @@
           <t>Kind: 120003</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -27481,6 +29771,11 @@
           <t>KIND 120003 — DEPRECATED</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">

--- a/kinds_Read_Origin.xlsx
+++ b/kinds_Read_Origin.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mục lục" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SKILL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SKILL.md" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="120001" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="120002" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="120002_1" sheetId="5" state="visible" r:id="rId5"/>
@@ -591,7 +591,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>SKILL</t>
+          <t>SKILL.md</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>KIND 220002_b_1 — Nội dung tương tự (2) [9~12] (Tách từ 220002_b)</t>
+          <t>KIND 220002_b_1 — Nội dung khớp poster/quảng cáo (Ảnh) [9]</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>KIND 220002_b_2 — Nội dung tương tự (2) [9~12] (Tách từ 220002_b)</t>
+          <t>KIND 220002_b_2 — Nội dung khớp biểu đồ/đồ thị (Ảnh) [10]</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>KIND 220002_b_3 — Nội dung tương tự (2) [9~12] (Tách từ 220002_b)</t>
+          <t>KIND 220002_b_3 — Nội dung khớp đoạn văn (Không ảnh) [11~12]</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>KIND 220003_a_1 — Chủ đề đoạn văn (1) [5~8] (Tách từ 220003_a)</t>
+          <t>KIND 220003_a_1 — Đây là gì? Chọn từ đơn (Ảnh) [5~6]</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>KIND 220003_a_2 — Chủ đề đoạn văn (1) [5~8] (Tách từ 220003_a)</t>
+          <t>KIND 220003_a_2 — Chủ đề/mục đích poster (Ảnh) [7~8]</t>
         </is>
       </c>
     </row>
@@ -9064,7 +9064,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>SKILL — Read_Origin</t>
+          <t>SKILL.md — Read_Origin</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -14865,7 +14865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -14891,7 +14891,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>KIND 220002_b_1 — Nội dung tương tự (2) [9~12] (Tách từ 220002_b)</t>
+          <t>KIND 220002_b_1 — Nội dung khớp poster/quảng cáo (Ảnh) [9]</t>
         </is>
       </c>
       <c r="B3" s="10" t="n"/>
@@ -14968,7 +14968,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Nội dung tương tự (2) [9~12]</t>
+          <t>Nội dung khớp poster/quảng cáo [9]</t>
         </is>
       </c>
     </row>
@@ -14980,7 +14980,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Similar content (2) [9~12]</t>
+          <t>Content matching — poster/ad (Image) [9]</t>
         </is>
       </c>
     </row>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Chọn đáp án có nội dung tương tự đoạn văn/biểu đồ. (Ấn vào ảnh để phóng to).</t>
+          <t>Xem poster/quảng cáo và chọn phát biểu khớp nội dung. (Ấn vào ảnh để phóng to).</t>
         </is>
       </c>
     </row>
@@ -15052,7 +15052,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Choose the answer that is similar to the paragraph/diagram. (Click image to enlarge).</t>
+          <t>Read the poster/ad image and choose the matching statement. (Click image to enlarge).</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Chủ đề thường gặp</t>
+          <t>Đặc điểm riêng — KHÁC với 220002_b_2 và 220002_b_3</t>
         </is>
       </c>
       <c r="B28" s="10" t="n"/>
@@ -15179,171 +15179,128 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>survey_statistics(25%), notice_event(20%), advertisement(15%), schedule(10%), chart_comparison(10%), infographic(10%), other(10%). Nội dung thiên về biểu đồ thống kê và thông báo/quảng cáo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+          <t>Dạng đọc poster/quảng cáo/thông báo sự kiện (Ảnh):</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>• q_image là poster, quảng cáo, thông báo sự kiện, tờ rơi — KHÔNG phải biểu đồ/đồ thị</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>• q_text rỗng — nội dung nằm hoàn toàn trong ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>• Nội dung poster chứa: tiêu đề sự kiện, thời gian, địa điểm, giá vé, điều kiện, ưu đãi</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>• Đáp án là câu dài (~25 ký tự) mô tả chi tiết từ poster</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>• Bẫy chính: thay đổi ngày/giờ/giá/điều kiện từ poster</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Chủ đề thường gặp</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>notice_event(30%), advertisement(25%), schedule(15%), travel_info(10%), service_info(10%), other(10%). Nội dung thiên về thông báo sự kiện và quảng cáo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Nhãn hệ thống</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>Nhãn</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>Giá trị</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>question_feature</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>`qf_graph_match`</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>text_format</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>`text_notice_poster`</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>answer_grammar</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>`ans_sentence_long`</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>Chiến lược bẫy</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>Bẫy</t>
-        </is>
-      </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>Tỷ lệ</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>`trap_number_shift`</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>60%</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Thay đổi con số/tỷ lệ so với dữ liệu thực trên biểu đồ</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>`trap_detail_distort`</t>
+          <t>question_feature</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Bóp méo chi tiết: đổi thời gian, địa điểm, đối tượng</t>
+          <t>`qf_content_match`</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>`trap_partial_truth`</t>
+          <t>text_format</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>45%</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Một phần đúng nhưng phần còn lại sai</t>
+          <t>`text_notice_poster`</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>`trap_shared_noun`</t>
+          <t>answer_grammar</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Dùng lại từ khóa từ biểu đồ/poster trong đáp án sai</t>
+          <t>`ans_sentence_long`</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>Cấu trúc bài đọc</t>
+          <t>Chiến lược bẫy</t>
         </is>
       </c>
       <c r="B43" s="10" t="n"/>
@@ -15353,56 +15310,94 @@
       <c r="F43" s="10" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>• q_image chứa biểu đồ, đồ thị, poster, hoặc thông báo</t>
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>Bẫy</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>• q_text có thể rỗng hoặc rất ngắn (phụ đề cho hình)</t>
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>`trap_detail_distort`</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Thay đổi thời gian, địa điểm, điều kiện cụ thể từ poster</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>• CẦN q_image_description mô tả chi tiết nội dung hình ảnh</t>
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>`trap_number_shift`</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Thay đổi giá vé, tỷ lệ giảm giá, số lượng từ poster</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>• Hình ảnh chứa số liệu, thời gian, địa điểm, điều kiện cụ thể</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>Cách mô tả ảnh (q_image_description)</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="n"/>
-      <c r="C48" s="10" t="n"/>
-      <c r="D48" s="10" t="n"/>
-      <c r="E48" s="10" t="n"/>
-      <c r="F48" s="10" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>Mô tả phải bao gồm: loại biểu đồ/thông báo, tiêu đề, tất cả số liệu/tỷ lệ, trục/nhãn, xu hướng chính, và mọi chi tiết quan trọng. Mô tả PHẢI đủ chi tiết để tạo đáp án đúng/sai mà không cần nhìn ảnh.</t>
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>`trap_partial_truth`</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Một phần đúng nhưng sai ở chi tiết cuối</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>`trap_shared_noun`</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Dùng lại từ khóa từ poster trong đáp án sai</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>Cấu trúc đáp án</t>
+          <t>Cấu trúc bài đọc</t>
         </is>
       </c>
       <c r="B50" s="10" t="n"/>
@@ -15414,246 +15409,336 @@
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>• 4 câu mô tả dài (~25 ký tự), dạng trần thuật</t>
+          <t>• q_image: ảnh poster/quảng cáo/thông báo (CÓ ảnh, KHÔNG phải biểu đồ)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>• Đáp án đúng: khớp chính xác một thông tin trên biểu đồ/poster</t>
+          <t>• q_text: rỗng ""</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>• Đáp án sai: thay đổi con số, đảo thứ tự, bóp méo chi tiết từ hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>Quy tắc bắt buộc</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="n"/>
-      <c r="C54" s="10" t="n"/>
-      <c r="D54" s="10" t="n"/>
-      <c r="E54" s="10" t="n"/>
-      <c r="F54" s="10" t="n"/>
+          <t>• count_question: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>• Poster chứa: tiêu đề, nội dung chính, ngày giờ, địa điểm, giá, điều kiện ưu đãi</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>1. Hình ảnh PHẢI có đủ thông tin chi tiết (số liệu, nhãn, tiêu đề) để phân biệt đáp án</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>2. q_image_description PHẢI mô tả đầy đủ mọi số liệu và chi tiết trên hình</t>
-        </is>
-      </c>
+          <t>• CẦN q_image_description mô tả đầy đủ nội dung poster</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Cách mô tả ảnh (q_image_description)</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>3. Ít nhất 2 đáp án sai PHẢI thay đổi con số/tỷ lệ (trap_number_shift)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>4. Ít nhất 1 đáp án sai PHẢI bóp méo chi tiết khác (thời gian, địa điểm, đối tượng)</t>
-        </is>
-      </c>
+          <t>Mô tả poster phải bao gồm: loại poster (행사 안내, 할인 광고, 모집 안내...), tiêu đề, nội dung chính, thời gian, địa điểm, giá vé/phí, điều kiện ưu đãi, số liên hệ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Cấu trúc đáp án — 1 câu (count_question = 1)</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>5. 4 đáp án phải cùng cấu trúc câu và độ dài tương đương</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="9" t="inlineStr">
+          <t>• 4 câu trần thuật dài (~25 ký tự)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>• Đáp án đúng: khớp chính xác 1 chi tiết cụ thể từ poster</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>• Đáp án sai: thay đổi chi tiết thời gian/địa điểm/giá/điều kiện</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>Quy tắc bắt buộc</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="10" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>1. q_image là poster/quảng cáo/thông báo — KHÔNG phải biểu đồ (biểu đồ là 220002_b_2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>2. q_text PHẢI rỗng ""</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>3. Poster phải chứa ít nhất 4 chi tiết cụ thể (ngày, giờ, địa điểm, giá) để tạo bẫy</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>4. q_image_description PHẢI liệt kê mọi chi tiết trên poster</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>5. 4 đáp án cùng cấu trúc câu và độ dài tương đương</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="9" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B60" s="10" t="n"/>
-      <c r="C60" s="10" t="n"/>
-      <c r="D60" s="10" t="n"/>
-      <c r="E60" s="10" t="n"/>
-      <c r="F60" s="10" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>{</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "q_image_description": "막대그래프: '직장인 출퇴근 수단 조사' — 지하철 45%, 버스 25%, 자가용 20%, 자전거 10%. 조사 대상: 서울 직장인 1,000명, 2024년 3월 조사.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "content": [{</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "q_text": "",</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "q_answer": [</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      "지하철을 이용하는 직장인이 가장 많다.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      "버스를 이용하는 직장인이 30%이다.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      "자가용을 이용하는 직장인이 자전거보다 적다.",</t>
-        </is>
-      </c>
+      <c r="B68" s="10" t="n"/>
+      <c r="C68" s="10" t="n"/>
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="10" t="n"/>
+      <c r="F68" s="10" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "이 조사는 부산 직장인을 대상으로 했다."</t>
+          <t>{</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ],</t>
+          <t xml:space="preserve">  "q_image_description": {</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_correct": 1</t>
+          <t xml:space="preserve">    "image": "포스터: '제5회 한국 음식 축제' 안내. 일시: 10월 15일(토)~16일(일), 장소: 서울 광장. 입장료: 무료. 주말에는 단체 할인 없음. 지하철 이용 시 입장권 1,000원 할인."</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  }]</t>
+          <t xml:space="preserve">  },</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">  "content": [{</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "q_text": "",</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "q_answer": [</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      "주말에는 단체 할인을 받을 수 있다.",</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      "이 행사는 이번에 처음 열리는 행사이다.",</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      "특별권을 사면 놀이 시설 이용료가 할인된다.",</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      "지하철을 타고 가면 입장권을 싸게 살 수 있다."</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ],</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "q_correct": 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  }]</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
           <t>}</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>• ① ✅ (đúng — 지하철 45%로 가장 많음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t>• ② trap_number_shift (25% → 30%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t>• ③ trap_detail_distort (자가용 20% &gt; 자전거 10%, đảo ngược)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>• ④ trap_detail_distort (서울 → 부산)</t>
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>• ④ ✅ (지하철 이용 시 입장권 1,000원 할인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="11" t="inlineStr">
+        <is>
+          <t>• ① trap_detail_distort (단체 할인 없음 → 받을 수 있다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t>• ② trap_number_shift (제5회 → 처음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t>• ③ trap_partial_truth (할인은 입장권에만 적용, 놀이 시설 아님)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="53">
     <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A46:F46"/>
     <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A74:F74"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A50:F50"/>
     <mergeCell ref="A56:F56"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A86:F86"/>
     <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A85:F85"/>
     <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A62:F62"/>
     <mergeCell ref="A53:F53"/>
     <mergeCell ref="A72:F72"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A81:F81"/>
     <mergeCell ref="A63:F63"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A44:F44"/>
     <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A83:F83"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A77:F77"/>
     <mergeCell ref="A64:F64"/>
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="A73:F73"/>
-    <mergeCell ref="A49:F49"/>
     <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A82:F82"/>
     <mergeCell ref="A60:F60"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A79:F79"/>
     <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A88:F88"/>
     <mergeCell ref="A78:F78"/>
     <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A87:F87"/>
     <mergeCell ref="A65:F65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15666,7 +15751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -15692,7 +15777,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>KIND 220002_b_2 — Nội dung tương tự (2) [9~12] (Tách từ 220002_b)</t>
+          <t>KIND 220002_b_2 — Nội dung khớp biểu đồ/đồ thị (Ảnh) [10]</t>
         </is>
       </c>
       <c r="B3" s="10" t="n"/>
@@ -15769,7 +15854,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Nội dung tương tự (2) [9~12]</t>
+          <t>Nội dung khớp biểu đồ/đồ thị [10]</t>
         </is>
       </c>
     </row>
@@ -15781,7 +15866,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Similar content (2) [9~12]</t>
+          <t>Content matching — chart/graph (Image) [10]</t>
         </is>
       </c>
     </row>
@@ -15841,7 +15926,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Chọn đáp án có nội dung tương tự đoạn văn/biểu đồ. (Ấn vào ảnh để phóng to).</t>
+          <t>Xem biểu đồ/đồ thị và chọn phát biểu khớp số liệu. (Ấn vào ảnh để phóng to).</t>
         </is>
       </c>
     </row>
@@ -15853,7 +15938,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Choose the answer that is similar to the paragraph/diagram. (Click image to enlarge).</t>
+          <t>Read the chart/graph image and choose the matching statement. (Click image to enlarge).</t>
         </is>
       </c>
     </row>
@@ -15964,7 +16049,7 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Chủ đề thường gặp</t>
+          <t>Đặc điểm riêng — KHÁC với 220002_b_1 và 220002_b_3</t>
         </is>
       </c>
       <c r="B28" s="10" t="n"/>
@@ -15976,171 +16061,128 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>survey_statistics(25%), notice_event(20%), advertisement(15%), schedule(10%), chart_comparison(10%), infographic(10%), other(10%). Nội dung thiên về biểu đồ thống kê và thông báo/quảng cáo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+          <t>Dạng đọc biểu đồ/đồ thị (Ảnh):</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>• q_image là biểu đồ, đồ thị, bảng thống kê — KHÔNG phải poster/quảng cáo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>• q_text rỗng — nội dung nằm hoàn toàn trong ảnh biểu đồ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>• Nội dung biểu đồ chứa: tiêu đề khảo sát, trục/nhãn, số liệu %, thứ hạng, so sánh</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>• Đáp án là câu dài (~31 ký tự) mô tả và so sánh số liệu</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>• Bẫy chính: đảo thứ hạng, thay đổi con số %, sai đối tượng so sánh</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Chủ đề thường gặp</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>survey_statistics(40%), chart_comparison(30%), infographic(15%), demographic_data(10%), other(5%). Nội dung thiên về khảo sát thống kê và so sánh số liệu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Nhãn hệ thống</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>Nhãn</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>Giá trị</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>question_feature</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>`qf_graph_match`</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>text_format</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>`text_notice_poster`</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>answer_grammar</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>`ans_sentence_long`</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>Chiến lược bẫy</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>Bẫy</t>
-        </is>
-      </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>Tỷ lệ</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>`trap_number_shift`</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>60%</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Thay đổi con số/tỷ lệ so với dữ liệu thực trên biểu đồ</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>`trap_detail_distort`</t>
+          <t>question_feature</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Bóp méo chi tiết: đổi thời gian, địa điểm, đối tượng</t>
+          <t>`qf_graph_match`</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>`trap_partial_truth`</t>
+          <t>text_format</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>45%</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Một phần đúng nhưng phần còn lại sai</t>
+          <t>`text_chart_graph`</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>`trap_shared_noun`</t>
+          <t>answer_grammar</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Dùng lại từ khóa từ biểu đồ/poster trong đáp án sai</t>
+          <t>`ans_sentence_long`</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>Cấu trúc bài đọc</t>
+          <t>Chiến lược bẫy</t>
         </is>
       </c>
       <c r="B43" s="10" t="n"/>
@@ -16150,56 +16192,94 @@
       <c r="F43" s="10" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>• q_image chứa biểu đồ, đồ thị, poster, hoặc thông báo</t>
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>Bẫy</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>• q_text có thể rỗng hoặc rất ngắn (phụ đề cho hình)</t>
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>`trap_number_shift`</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Thay đổi con số/tỷ lệ % so với biểu đồ</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>• CẦN q_image_description mô tả chi tiết nội dung hình ảnh</t>
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>`trap_detail_distort`</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Đảo thứ hạng: "A nhiều hơn B" → "B nhiều hơn A"</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>• Hình ảnh chứa số liệu, thời gian, địa điểm, điều kiện cụ thể</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>Cách mô tả ảnh (q_image_description)</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="n"/>
-      <c r="C48" s="10" t="n"/>
-      <c r="D48" s="10" t="n"/>
-      <c r="E48" s="10" t="n"/>
-      <c r="F48" s="10" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>Mô tả phải bao gồm: loại biểu đồ/thông báo, tiêu đề, tất cả số liệu/tỷ lệ, trục/nhãn, xu hướng chính, và mọi chi tiết quan trọng. Mô tả PHẢI đủ chi tiết để tạo đáp án đúng/sai mà không cần nhìn ảnh.</t>
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>`trap_partial_truth`</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Đúng về xu hướng nhưng sai con số cụ thể</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>`trap_subject_swap`</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Gán số liệu cho sai nhóm đối tượng</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>Cấu trúc đáp án</t>
+          <t>Cấu trúc bài đọc</t>
         </is>
       </c>
       <c r="B50" s="10" t="n"/>
@@ -16211,246 +16291,352 @@
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>• 4 câu mô tả dài (~25 ký tự), dạng trần thuật</t>
+          <t>• q_image: ảnh biểu đồ/đồ thị (막대그래프, 원그래프, 꺾은선그래프, 표)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>• Đáp án đúng: khớp chính xác một thông tin trên biểu đồ/poster</t>
+          <t>• q_text: rỗng ""</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>• Đáp án sai: thay đổi con số, đảo thứ tự, bóp méo chi tiết từ hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>Quy tắc bắt buộc</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="n"/>
-      <c r="C54" s="10" t="n"/>
-      <c r="D54" s="10" t="n"/>
-      <c r="E54" s="10" t="n"/>
-      <c r="F54" s="10" t="n"/>
+          <t>• count_question: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>• Biểu đồ chứa: tiêu đề, trục/nhãn, tỷ lệ %, số liệu, đối tượng khảo sát</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>1. Hình ảnh PHẢI có đủ thông tin chi tiết (số liệu, nhãn, tiêu đề) để phân biệt đáp án</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>2. q_image_description PHẢI mô tả đầy đủ mọi số liệu và chi tiết trên hình</t>
-        </is>
-      </c>
+          <t>• CẦN q_image_description mô tả đầy đủ mọi số liệu</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Cách mô tả ảnh (q_image_description)</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>3. Ít nhất 2 đáp án sai PHẢI thay đổi con số/tỷ lệ (trap_number_shift)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>4. Ít nhất 1 đáp án sai PHẢI bóp méo chi tiết khác (thời gian, địa điểm, đối tượng)</t>
-        </is>
-      </c>
+          <t>Mô tả biểu đồ phải bao gồm: loại biểu đồ (막대/원/꺾은선), tiêu đề, tất cả số liệu/tỷ lệ, trục/nhãn, đối tượng khảo sát, thời gian khảo sát, xu hướng chính. Mô tả PHẢI đủ chi tiết để so sánh các giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Cấu trúc đáp án — 1 câu (count_question = 1)</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>5. 4 đáp án phải cùng cấu trúc câu và độ dài tương đương</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="9" t="inlineStr">
+          <t>• 4 câu trần thuật dài (~31 ký tự), thường chứa so sánh giữa các mục</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>• Cấu trúc đáp án thường dùng: "A가/보다 B보다 더 많다/적다", "전체의 반이 넘다", "가장 많다/적다"</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>• Đáp án đúng: khớp chính xác thứ hạng/số liệu trên biểu đồ</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>• Đáp án sai: đảo thứ hạng, thay đổi %, gán sai nhóm</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>Quy tắc bắt buộc</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="10" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>1. q_image là biểu đồ/đồ thị/bảng thống kê — KHÔNG phải poster (poster là 220002_b_1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>2. q_text PHẢI rỗng ""</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>3. Biểu đồ phải có ít nhất 3 hạng mục để tạo đủ bẫy so sánh</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>4. q_image_description PHẢI liệt kê tất cả con số/tỷ lệ trên biểu đồ</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>5. Ít nhất 2 đáp án sai PHẢI liên quan đến so sánh sai giữa các hạng mục</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>6. 4 đáp án cùng cấu trúc câu và độ dài tương đương</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B60" s="10" t="n"/>
-      <c r="C60" s="10" t="n"/>
-      <c r="D60" s="10" t="n"/>
-      <c r="E60" s="10" t="n"/>
-      <c r="F60" s="10" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>{</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "q_image_description": "막대그래프: '직장인 출퇴근 수단 조사' — 지하철 45%, 버스 25%, 자가용 20%, 자전거 10%. 조사 대상: 서울 직장인 1,000명, 2024년 3월 조사.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "content": [{</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "q_text": "",</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "q_answer": [</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      "지하철을 이용하는 직장인이 가장 많다.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      "버스를 이용하는 직장인이 30%이다.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      "자가용을 이용하는 직장인이 자전거보다 적다.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      "이 조사는 부산 직장인을 대상으로 했다."</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ],</t>
-        </is>
-      </c>
+      <c r="B70" s="10" t="n"/>
+      <c r="C70" s="10" t="n"/>
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="10" t="n"/>
+      <c r="F70" s="10" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_correct": 1</t>
+          <t>{</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  }]</t>
+          <t xml:space="preserve">  "q_image_description": {</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">    "image": "원그래프: '반려동물을 어떻게 데려왔습니까?' — 주인 없는 동물 데려옴 10%, 인터넷에서 구매 15%, 가게에서 구매 25%, 아는 사람한테서 받음 50%. 조사 대상: 반려동물 주인 500명."</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  },</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  "content": [{</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "q_text": "",</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "q_answer": [</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      "주인 없는 동물을 데려와 키우는 사람이 가장 적다.",</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      "인터넷에서 산 사람이 가게에서 산 사람보다 더 많다.",</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      "가게에서 산 사람보다 아는 사람한테서 받은 사람이 더 적다.",</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      "아는 사람한테서 동물을 데리고 온 사람은 전체의 반이 넘는다."</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ],</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "q_correct": 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  }]</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
           <t>}</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>• ① ✅ (đúng — 지하철 45%로 가장 많음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t>• ② trap_number_shift (25% → 30%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t>• ③ trap_detail_distort (자가용 20% &gt; 자전거 10%, đảo ngược)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>• ④ trap_detail_distort (서울 → 부산)</t>
+    <row r="87">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t>• ① ✅ (주인 없는 동물 10%로 가장 적음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t>• ② trap_detail_distort (인터넷 15% &lt; 가게 25%, 순서 반대)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t>• ③ trap_detail_distort (가게 25% &lt; 아는 사람 50%, 순서 반대)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t>• ④ trap_number_shift (50% = 반, 넘지 않음)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="55">
     <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A90:F90"/>
     <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A74:F74"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A50:F50"/>
     <mergeCell ref="A56:F56"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A85:F85"/>
     <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A62:F62"/>
     <mergeCell ref="A53:F53"/>
     <mergeCell ref="A72:F72"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A81:F81"/>
     <mergeCell ref="A63:F63"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A44:F44"/>
     <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A83:F83"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A77:F77"/>
     <mergeCell ref="A64:F64"/>
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="A73:F73"/>
-    <mergeCell ref="A49:F49"/>
     <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A82:F82"/>
     <mergeCell ref="A60:F60"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A79:F79"/>
     <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A88:F88"/>
     <mergeCell ref="A78:F78"/>
     <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A87:F87"/>
     <mergeCell ref="A65:F65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16463,7 +16649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -16489,7 +16675,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>KIND 220002_b_3 — Nội dung tương tự (2) [9~12] (Tách từ 220002_b)</t>
+          <t>KIND 220002_b_3 — Nội dung khớp đoạn văn (Không ảnh) [11~12]</t>
         </is>
       </c>
       <c r="B3" s="10" t="n"/>
@@ -16566,7 +16752,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Nội dung tương tự (2) [9~12]</t>
+          <t>Nội dung khớp đoạn văn [11~12]</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16764,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Similar content (2) [9~12]</t>
+          <t>Content matching — text passage (No image) [11~12]</t>
         </is>
       </c>
     </row>
@@ -16638,7 +16824,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Chọn đáp án có nội dung tương tự đoạn văn/biểu đồ. (Ấn vào ảnh để phóng to).</t>
+          <t>Đọc đoạn văn và chọn phát biểu có nội dung khớp.</t>
         </is>
       </c>
     </row>
@@ -16650,7 +16836,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Choose the answer that is similar to the paragraph/diagram. (Click image to enlarge).</t>
+          <t>Read the passage and choose the statement with matching content.</t>
         </is>
       </c>
     </row>
@@ -16761,7 +16947,7 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Chủ đề thường gặp</t>
+          <t>Đặc điểm riêng — KHÁC với 220002_b_1 và 220002_b_2</t>
         </is>
       </c>
       <c r="B28" s="10" t="n"/>
@@ -16773,171 +16959,128 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>survey_statistics(25%), notice_event(20%), advertisement(15%), schedule(10%), chart_comparison(10%), infographic(10%), other(10%). Nội dung thiên về biểu đồ thống kê và thông báo/quảng cáo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+          <t>Dạng đọc đoạn văn thuần text (Không ảnh):</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>• KHÔNG có ảnh — q_image rỗng</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>• Bài đọc nằm trong q_text (đoạn văn dài 3-6 câu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>• Đáp án là câu ngắn hơn (~23 ký tự) so với 220002_b_1/b_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>• Nội dung đoạn văn thường là thông tin, giải thích, kể chuyện — KHÔNG phải số liệu thống kê</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>• Bẫy chính: bóp méo chi tiết nội dung đoạn văn</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Chủ đề thường gặp</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>culture_knowledge(25%), daily_life(20%), science_tech(15%), psychology_behavior(15%), environment_society(10%), other(15%). Nội dung thiên về kiến thức tổng hợp và đời sống.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Nhãn hệ thống</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>Nhãn</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>Giá trị</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>question_feature</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>`qf_graph_match`</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>text_format</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>`text_notice_poster`</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>answer_grammar</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>`ans_sentence_long`</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>Chiến lược bẫy</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>Bẫy</t>
-        </is>
-      </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>Tỷ lệ</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>`trap_number_shift`</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>60%</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Thay đổi con số/tỷ lệ so với dữ liệu thực trên biểu đồ</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>`trap_detail_distort`</t>
+          <t>question_feature</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Bóp méo chi tiết: đổi thời gian, địa điểm, đối tượng</t>
+          <t>`qf_content_match`</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>`trap_partial_truth`</t>
+          <t>text_format</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>45%</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Một phần đúng nhưng phần còn lại sai</t>
+          <t>`text_paragraph_short`</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>`trap_shared_noun`</t>
+          <t>answer_grammar</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Dùng lại từ khóa từ biểu đồ/poster trong đáp án sai</t>
+          <t>`ans_sentence_plain`</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>Cấu trúc bài đọc</t>
+          <t>Chiến lược bẫy</t>
         </is>
       </c>
       <c r="B43" s="10" t="n"/>
@@ -16947,278 +17090,385 @@
       <c r="F43" s="10" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>• q_image chứa biểu đồ, đồ thị, poster, hoặc thông báo</t>
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>Bẫy</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>• q_text có thể rỗng hoặc rất ngắn (phụ đề cho hình)</t>
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>`trap_partial_truth`</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Nửa đúng nửa sai — đúng chủ đề nhưng sai chi tiết</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>• CẦN q_image_description mô tả chi tiết nội dung hình ảnh</t>
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>`trap_detail_distort`</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Thay đổi 1 chi tiết cụ thể từ đoạn văn</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>• Hình ảnh chứa số liệu, thời gian, địa điểm, điều kiện cụ thể</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>Cách mô tả ảnh (q_image_description)</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="n"/>
-      <c r="C48" s="10" t="n"/>
-      <c r="D48" s="10" t="n"/>
-      <c r="E48" s="10" t="n"/>
-      <c r="F48" s="10" t="n"/>
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>`trap_wrong_inference`</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Suy luận hợp lý nhưng không có trong bài</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>`trap_subject_swap`</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Gán hành động/đặc điểm cho sai đối tượng</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>Mô tả phải bao gồm: loại biểu đồ/thông báo, tiêu đề, tất cả số liệu/tỷ lệ, trục/nhãn, xu hướng chính, và mọi chi tiết quan trọng. Mô tả PHẢI đủ chi tiết để tạo đáp án đúng/sai mà không cần nhìn ảnh.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>Cấu trúc đáp án</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="10" t="n"/>
-      <c r="E50" s="10" t="n"/>
-      <c r="F50" s="10" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>• 4 câu mô tả dài (~25 ký tự), dạng trần thuật</t>
-        </is>
-      </c>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>`trap_overgeneralize`</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Khái quát hóa quá mức từ nội dung cụ thể</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>Cấu trúc bài đọc</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>• Đáp án đúng: khớp chính xác một thông tin trên biểu đồ/poster</t>
+          <t>• q_image: rỗng "" — KHÔNG có ảnh</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>• Đáp án sai: thay đổi con số, đảo thứ tự, bóp méo chi tiết từ hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>Quy tắc bắt buộc</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="n"/>
-      <c r="C54" s="10" t="n"/>
-      <c r="D54" s="10" t="n"/>
-      <c r="E54" s="10" t="n"/>
-      <c r="F54" s="10" t="n"/>
+          <t>• q_text: đoạn văn dài (~100-200 ký tự, 3-6 câu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>• count_question: 1</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>1. Hình ảnh PHẢI có đủ thông tin chi tiết (số liệu, nhãn, tiêu đề) để phân biệt đáp án</t>
+          <t>• Đoạn văn mang tính giải thích, thông tin, kể chuyện</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>2. q_image_description PHẢI mô tả đầy đủ mọi số liệu và chi tiết trên hình</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>3. Ít nhất 2 đáp án sai PHẢI thay đổi con số/tỷ lệ (trap_number_shift)</t>
-        </is>
-      </c>
+          <t>• KHÔNG cần q_image_description</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>Cấu trúc đáp án — 1 câu (count_question = 1)</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>4. Ít nhất 1 đáp án sai PHẢI bóp méo chi tiết khác (thời gian, địa điểm, đối tượng)</t>
+          <t>• 4 câu trần thuật (~23 ký tự), ngắn hơn dạng biểu đồ</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>5. 4 đáp án phải cùng cấu trúc câu và độ dài tương đương</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="9" t="inlineStr">
+          <t>• Đáp án đúng: khớp chính xác 1 thông tin cụ thể trong đoạn văn</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>• Đáp án sai: bóp méo chi tiết, suy luận sai, hoán đổi chủ thể</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>Quy tắc bắt buộc</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>1. KHÔNG có ảnh — q_image rỗng, bài đọc nằm trong q_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>2. q_text PHẢI là đoạn văn đủ dài (~100-200 ký tự) với nhiều chi tiết cụ thể</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>3. Đoạn văn phải chứa ít nhất 3 thông tin cụ thể để tạo đủ bẫy</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>4. Đáp án sai phải bóp méo chi tiết từ đoạn văn — KHÔNG phải thay đổi con số (khác b_2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>5. 4 đáp án cùng cấu trúc câu và độ dài tương đương</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>6. Độ khó cao hơn b_1 và b_2 vì đoạn văn dài và cần hiểu nội dung</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="9" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B60" s="10" t="n"/>
-      <c r="C60" s="10" t="n"/>
-      <c r="D60" s="10" t="n"/>
-      <c r="E60" s="10" t="n"/>
-      <c r="F60" s="10" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>{</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "q_image_description": "막대그래프: '직장인 출퇴근 수단 조사' — 지하철 45%, 버스 25%, 자가용 20%, 자전거 10%. 조사 대상: 서울 직장인 1,000명, 2024년 3월 조사.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "content": [{</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "q_text": "",</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "q_answer": [</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      "지하철을 이용하는 직장인이 가장 많다.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      "버스를 이용하는 직장인이 30%이다.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      "자가용을 이용하는 직장인이 자전거보다 적다.",</t>
-        </is>
-      </c>
+      <c r="B68" s="10" t="n"/>
+      <c r="C68" s="10" t="n"/>
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="10" t="n"/>
+      <c r="F68" s="10" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "이 조사는 부산 직장인을 대상으로 했다."</t>
+          <t>{</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ],</t>
+          <t xml:space="preserve">  "content": [{</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_correct": 1</t>
+          <t xml:space="preserve">    "q_text": "최근 70～80년대를 경험해 볼 수 있는 문화 공간이 생겼다. 서울시에서 새로 문을 연 '추억극장'이 바로 그곳이다. 입장료 2,000원만 내면 옛날 영화를 볼 수 있고 그 시절의 간식도 먹어 볼 수 있다. 특히 부모님과 함께 오는 가족들이 많다.",</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  }]</t>
+          <t xml:space="preserve">    "q_answer": [</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">      "이곳에서 옛날 영화 포스터를 살 수 있다.",</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      "얼마 전 추억의 문화 공간이 새로 만들어졌다.",</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      "추억극장은 입장료가 없기 때문에 인기가 많다.",</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      "추억극장에서는 최근에 나온 영화도 볼 수 있다."</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ],</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "q_correct": 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  }]</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
           <t>}</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>• ① ✅ (đúng — 지하철 45%로 가장 많음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t>• ② trap_number_shift (25% → 30%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t>• ③ trap_detail_distort (자가용 20% &gt; 자전거 10%, đảo ngược)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>• ④ trap_detail_distort (서울 → 부산)</t>
+    <row r="82">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>• ② ✅ (새로 문을 연 = 얼마 전 새로 만들어졌다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>• ① trap_wrong_inference (영화는 볼 수 있지만 포스터를 산다는 말 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>• ③ trap_detail_distort (입장료 2,000원 → 없다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>• ④ trap_detail_distort (옛날 영화 → 최근 영화)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="49">
     <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A84:F84"/>
     <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A74:F74"/>
     <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A50:F50"/>
     <mergeCell ref="A56:F56"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A85:F85"/>
     <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A62:F62"/>
     <mergeCell ref="A53:F53"/>
@@ -17229,22 +17479,23 @@
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A44:F44"/>
     <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A83:F83"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A77:F77"/>
     <mergeCell ref="A64:F64"/>
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="A73:F73"/>
-    <mergeCell ref="A49:F49"/>
     <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A82:F82"/>
     <mergeCell ref="A60:F60"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A79:F79"/>
     <mergeCell ref="A61:F61"/>
     <mergeCell ref="A78:F78"/>
     <mergeCell ref="A69:F69"/>
@@ -18733,7 +18984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -18759,7 +19010,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>KIND 220003_a_1 — Chủ đề đoạn văn (1) [5~8] (Tách từ 220003_a)</t>
+          <t>KIND 220003_a_1 — Đây là gì? Chọn từ đơn (Ảnh) [5~6]</t>
         </is>
       </c>
       <c r="B3" s="10" t="n"/>
@@ -18836,7 +19087,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Chủ đề đoạn văn (1) [5~8]</t>
+          <t>Đây là gì? — Chọn từ đơn [5~6]</t>
         </is>
       </c>
     </row>
@@ -18848,7 +19099,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Main idea (1) [5~8]</t>
+          <t>What is this? — Choose single word (Image) [5~6]</t>
         </is>
       </c>
     </row>
@@ -18908,7 +19159,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Chọn chủ đề cho nội dung trong đề bài. (Ấn vào ảnh để phóng to).</t>
+          <t>Xem ảnh/biển báo và chọn đúng tên gọi (từ đơn). (Ấn vào ảnh để phóng to).</t>
         </is>
       </c>
     </row>
@@ -18920,7 +19171,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Choose a topic for the content. (Click image to enlarge).</t>
+          <t>Look at the image/sign and choose the correct name (single word). (Click image to enlarge).</t>
         </is>
       </c>
     </row>
@@ -19035,7 +19286,7 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Chủ đề thường gặp</t>
+          <t>Đặc điểm riêng — KHÁC với 220003_a_2</t>
         </is>
       </c>
       <c r="B28" s="10" t="n"/>
@@ -19047,196 +19298,191 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>product_ad(18%), event_notice(15%), service_info(12%), sign_label(10%), public_notice(10%), schedule(8%), menu_price(7%), other(20%). Nội dung đa dạng, gắn với đời sống thực tế.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+          <t>Dạng "Đây là gì?" — Đáp án là TỪ ĐƠN (~2 âm tiết):</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>• q_image là ảnh đồ vật, biển báo, nơi chốn cụ thể</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>• Đáp án là từ đơn danh từ rất ngắn: 신문, 사전, 시계, 연필, 병원, 학원, 박물관, 대사관</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>• Hỏi "Đây là CÁI GÌ?" hoặc "Đây là ĐÂU?" — nhận diện vật/nơi cụ thể</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>• Dễ nhất trong nhóm 220003 — chỉ cần biết từ vựng</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>So sánh với 220003_a_2: 220003_a_2 hỏi chủ đề/mục đích (환경 보호, 상품 안내) — trừu tượng hơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Chủ đề thường gặp</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>object_item(35%), place_location(30%), sign_label(20%), tool_equipment(10%), other(5%). Nội dung thiên về đồ vật và địa điểm cụ thể.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Nhãn hệ thống</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>Nhãn</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>Giá trị</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>question_feature</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>`qf_topic_identify`</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>text_format</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>`text_notice_poster`</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>answer_grammar</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>`ans_noun_phrase`</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>Chiến lược bẫy</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>Bẫy</t>
-        </is>
-      </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>Tỷ lệ</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>`trap_similar_word`</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Dùng danh từ cùng lĩnh vực/category nhưng sai chủ đề</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
+          <t>question_feature</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>`qf_object_identify`</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>text_format</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>`text_notice_poster`</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>answer_grammar</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>`ans_single_noun` (~2 âm tiết)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Chiến lược bẫy</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>Bẫy</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>`trap_similar_word`</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Danh từ cùng **nhóm vật/nơi** nhưng sai: 시계→달력, 병원→학원→박물관</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
           <t>`trap_shared_noun`</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Dùng từ xuất hiện trên biển/poster nhưng không phải chủ đề chính</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>Cấu trúc bài đọc</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="10" t="n"/>
-      <c r="E41" s="10" t="n"/>
-      <c r="F41" s="10" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>• q_image chứa hình biển báo, quảng cáo, thông báo, hoặc poster</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>• q_text rỗng (nội dung nằm hoàn toàn trong hình ảnh)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>• CẦN q_image_description mô tả chi tiết nội dung trên hình</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>• Hình ảnh chứa từ khóa, hình vẽ minh họa gợi ý chủ đề</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>Cách mô tả ảnh (q_image_description)</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="10" t="n"/>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n"/>
-      <c r="F46" s="10" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>Mô tả phải bao gồm: loại hình ảnh (biển báo/poster/quảng cáo), text trên hình, hình minh họa, bố cục, và mọi chi tiết quan trọng giúp nhận diện chủ đề. Mô tả PHẢI đủ rõ để xác định chủ đề chính.</t>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Từ liên quan đến hình ảnh nhưng không phải đáp án chính</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>Cấu trúc đáp án</t>
+          <t>Cấu trúc bài đọc</t>
         </is>
       </c>
       <c r="B48" s="10" t="n"/>
@@ -19248,204 +19494,302 @@
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>• 4 danh từ/cụm danh từ ngắn (~2-4 âm tiết)</t>
+          <t>• q_image: ảnh đồ vật, biển báo, tòa nhà, sản phẩm — hình cụ thể, rõ ràng</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>• Đáp án đúng: danh từ mô tả chính xác chủ đề/mục đích của biển/poster</t>
+          <t>• q_text: rỗng ""</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>• Đáp án sai: danh từ cùng lĩnh vực hoặc liên quan bề mặt</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>Quy tắc bắt buộc</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="n"/>
-      <c r="C52" s="10" t="n"/>
-      <c r="D52" s="10" t="n"/>
-      <c r="E52" s="10" t="n"/>
-      <c r="F52" s="10" t="n"/>
+          <t>• count_question: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>• Ảnh thường có: hình minh họa đồ vật + text ngắn (tên sản phẩm, biển hiệu)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>1. Hình ảnh PHẢI rõ ràng về chủ đề, có đủ gợi ý (text + hình minh họa)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>2. q_image_description PHẢI mô tả đầy đủ text và hình minh họa trên ảnh</t>
-        </is>
-      </c>
+          <t>• CẦN q_image_description mô tả hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Cách mô tả ảnh (q_image_description)</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>3. 4 đáp án PHẢI đều là danh từ ngắn, cùng độ dài tương đương</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>4. Ít nhất 2 đáp án sai PHẢI là danh từ cùng lĩnh vực/category (trap_similar_word)</t>
-        </is>
-      </c>
+          <t>Mô tả ngắn gọn: loại hình (đồ vật/biển báo/tòa nhà), hình dáng, text trên hình, đặc điểm nhận diện. Ảnh thường đơn giản, dễ nhận diện.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Cấu trúc đáp án — 1 câu (count_question = 1)</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>5. Ít nhất 1 đáp án sai PHẢI dùng từ xuất hiện trên hình nhưng không phải chủ đề chính</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="9" t="inlineStr">
+          <t>• 4 từ đơn danh từ rất ngắn (~2 âm tiết): 신문, 사전, 시계, 연필</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>• Đáp án đúng: tên chính xác của vật/nơi trong ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>• Đáp án sai: từ đơn cùng nhóm (đồ vật khác, nơi khác) nhưng SAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>• 4 đáp án PHẢI cùng nhóm ngữ nghĩa (đều là đồ vật, hoặc đều là nơi chốn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>Quy tắc bắt buộc</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>1. Đáp án là từ đơn (~2 âm tiết) — KHÔNG phải cụm từ (cụm từ là 220003_a_2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>2. 4 đáp án PHẢI cùng nhóm ngữ nghĩa: đều là đồ vật, hoặc đều là nơi chốn, hoặc đều là loại thức ăn</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>3. Ảnh phải rõ ràng, dễ nhận diện — đây là dạng dễ nhất</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>4. q_text PHẢI rỗng ""</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>5. q_image_description mô tả đồ vật/biển hiệu cụ thể</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="9" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
-      <c r="E58" s="10" t="n"/>
-      <c r="F58" s="10" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="B67" s="10" t="n"/>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="10" t="n"/>
+      <c r="E67" s="10" t="n"/>
+      <c r="F67" s="10" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
         <is>
           <t>{</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "q_image_description": "포스터: 상단에 '시간을 알려 주는 친구' 텍스트, 중앙에 다양한 손목시계 이미지 3개, 하단에 '30% 할인 — 이번 주만!' 문구. 밝은 파란색 배경.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  "q_image_description": {</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "image": "Hình ảnh tờ báo với tiêu đề tiếng Hàn, nhiều cột chữ, ảnh tin tức ở giữa. Phía trên có ngày tháng và tên báo."</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  },</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  "content": [{</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    "q_text": "",</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "q_answer": ["시계", "달력", "전화기", "가방"],</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="12" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "q_answer": ["신문", "사전", "시계", "연필"],</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    "q_correct": 1</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  }]</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="12" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
         <is>
           <t>}</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t>• ① 시계 ✅ (đúng — 손목시계 이미지와 "시간을 알려 주는 친구")</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t>• ② 달력 (trap_similar_word — 시간 관련 물건이지만 시계가 아님)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t>• ③ 전화기 (trap_similar_word — 전자기기 category)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t>• ④ 가방 (trap_shared_noun — 착용하는 물건이지만 무관)</t>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>• ① 신문 ✅ (tờ báo — đúng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>• ② 사전 (trap_similar_word — sách/tài liệu in nhưng là từ điển)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>• ③ 시계 (trap_similar_word — đồ vật khác hoàn toàn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>• ④ 연필 (trap_similar_word — đồ vật khác hoàn toàn)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="A41:F41"/>
+  <mergeCells count="49">
     <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A46:F46"/>
     <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A74:F74"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A50:F50"/>
     <mergeCell ref="A56:F56"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A62:F62"/>
     <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A72:F72"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A81:F81"/>
     <mergeCell ref="A63:F63"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A48:F48"/>
     <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A77:F77"/>
     <mergeCell ref="A64:F64"/>
     <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A73:F73"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A82:F82"/>
     <mergeCell ref="A60:F60"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A79:F79"/>
     <mergeCell ref="A61:F61"/>
     <mergeCell ref="A69:F69"/>
     <mergeCell ref="A65:F65"/>
@@ -19460,7 +19804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -19486,7 +19830,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>KIND 220003_a_2 — Chủ đề đoạn văn (1) [5~8] (Tách từ 220003_a)</t>
+          <t>KIND 220003_a_2 — Chủ đề/mục đích poster (Ảnh) [7~8]</t>
         </is>
       </c>
       <c r="B3" s="10" t="n"/>
@@ -19563,7 +19907,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Chủ đề đoạn văn (1) [5~8]</t>
+          <t>Chủ đề/mục đích poster [7~8]</t>
         </is>
       </c>
     </row>
@@ -19575,7 +19919,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Main idea (1) [5~8]</t>
+          <t>Topic/purpose of poster (Image) [7~8]</t>
         </is>
       </c>
     </row>
@@ -19635,7 +19979,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Chọn chủ đề cho nội dung trong đề bài. (Ấn vào ảnh để phóng to).</t>
+          <t>Xem poster/thông báo và chọn chủ đề/mục đích (cụm từ). (Ấn vào ảnh để phóng to).</t>
         </is>
       </c>
     </row>
@@ -19647,7 +19991,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Choose a topic for the content. (Click image to enlarge).</t>
+          <t>Look at the poster/notice and choose the topic/purpose (phrase). (Click image to enlarge).</t>
         </is>
       </c>
     </row>
@@ -19758,7 +20102,7 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Chủ đề thường gặp</t>
+          <t>Đặc điểm riêng — KHÁC với 220003_a_1</t>
         </is>
       </c>
       <c r="B28" s="10" t="n"/>
@@ -19770,406 +20114,516 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>product_ad(18%), event_notice(15%), service_info(12%), sign_label(10%), public_notice(10%), schedule(8%), menu_price(7%), other(20%). Nội dung đa dạng, gắn với đời sống thực tế.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+          <t>Dạng "Về chủ đề gì?" — Đáp án là CỤM TỪ (~4-5 âm tiết):</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>• q_image là ảnh poster, thông báo, quảng cáo, biểu ngữ</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>• Đáp án là cụm danh từ: 환경 보호, 상품 안내, 모집 안내, 날씨 정보, 여행 계획, 사용 방법, 문의 방법</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>• Hỏi "Đây là về CHỦ ĐỀ GÌ?" — nhận diện mục đích/chủ đề trừu tượng</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>• Khó hơn 220003_a_1 vì cần hiểu mục đích chứ không chỉ nhận diện vật</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>So sánh với 220003_a_1: 220003_a_1 hỏi "Đây là CÁI GÌ?" — đáp án là từ đơn cụ thể (신문, 병원)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Chủ đề thường gặp</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>public_notice(25%), product_ad(20%), event_notice(20%), service_info(15%), recruitment(10%), other(10%). Nội dung thiên về poster và thông báo có mục đích rõ ràng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Nhãn hệ thống</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>Nhãn</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>Giá trị</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>question_feature</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>`qf_topic_identify`</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>text_format</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>`text_notice_poster`</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>answer_grammar</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>`ans_noun_phrase`</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>Chiến lược bẫy</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>Bẫy</t>
-        </is>
-      </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>Tỷ lệ</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>`trap_similar_word`</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Dùng danh từ cùng lĩnh vực/category nhưng sai chủ đề</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
+          <t>question_feature</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>`qf_topic_identify`</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>text_format</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>`text_notice_poster`</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>answer_grammar</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>`ans_noun_phrase` (~4-5 âm tiết)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Chiến lược bẫy</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>Bẫy</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>`trap_similar_word`</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Cụm từ cùng lĩnh vực nhưng sai mục đích: 상품 안내→모집 안내→문의 방법</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
           <t>`trap_shared_noun`</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Dùng từ xuất hiện trên biển/poster nhưng không phải chủ đề chính</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Dùng từ xuất hiện trên poster nhưng không phải chủ đề chính</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>`trap_partial_truth`</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Chủ đề liên quan nhưng không phải mục đích chính</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="10" t="n"/>
-      <c r="E41" s="10" t="n"/>
-      <c r="F41" s="10" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>• q_image chứa hình biển báo, quảng cáo, thông báo, hoặc poster</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>• q_text rỗng (nội dung nằm hoàn toàn trong hình ảnh)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>• CẦN q_image_description mô tả chi tiết nội dung trên hình</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>• Hình ảnh chứa từ khóa, hình vẽ minh họa gợi ý chủ đề</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>Cách mô tả ảnh (q_image_description)</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="10" t="n"/>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n"/>
-      <c r="F46" s="10" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>Mô tả phải bao gồm: loại hình ảnh (biển báo/poster/quảng cáo), text trên hình, hình minh họa, bố cục, và mọi chi tiết quan trọng giúp nhận diện chủ đề. Mô tả PHẢI đủ rõ để xác định chủ đề chính.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>Cấu trúc đáp án</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="n"/>
-      <c r="C48" s="10" t="n"/>
-      <c r="D48" s="10" t="n"/>
-      <c r="E48" s="10" t="n"/>
-      <c r="F48" s="10" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>• 4 danh từ/cụm danh từ ngắn (~2-4 âm tiết)</t>
-        </is>
-      </c>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>• Đáp án đúng: danh từ mô tả chính xác chủ đề/mục đích của biển/poster</t>
+          <t>• q_image: ảnh poster, thông báo, quảng cáo, biểu ngữ — có nội dung text + hình minh họa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>• Đáp án sai: danh từ cùng lĩnh vực hoặc liên quan bề mặt</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>Quy tắc bắt buộc</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="n"/>
-      <c r="C52" s="10" t="n"/>
-      <c r="D52" s="10" t="n"/>
-      <c r="E52" s="10" t="n"/>
-      <c r="F52" s="10" t="n"/>
+          <t>• q_text: rỗng ""</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>• count_question: 1</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>1. Hình ảnh PHẢI rõ ràng về chủ đề, có đủ gợi ý (text + hình minh họa)</t>
+          <t>• Poster thường có: tiêu đề rõ ràng, hình minh họa, nội dung mô tả, thông tin liên hệ</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>2. q_image_description PHẢI mô tả đầy đủ text và hình minh họa trên ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>3. 4 đáp án PHẢI đều là danh từ ngắn, cùng độ dài tương đương</t>
-        </is>
-      </c>
+          <t>• CẦN q_image_description mô tả nội dung poster</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>Cách mô tả ảnh (q_image_description)</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>4. Ít nhất 2 đáp án sai PHẢI là danh từ cùng lĩnh vực/category (trap_similar_word)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>5. Ít nhất 1 đáp án sai PHẢI dùng từ xuất hiện trên hình nhưng không phải chủ đề chính</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="9" t="inlineStr">
+          <t>Mô tả poster bao gồm: loại poster (안내문, 광고, 모집, 캠페인), tiêu đề, nội dung chính, hình minh họa, từ khóa nổi bật. Mô tả phải đủ để xác định chủ đề/mục đích chính.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>Cấu trúc đáp án — 1 câu (count_question = 1)</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>• 4 cụm danh từ (~4-5 âm tiết): 환경 보호, 상품 안내, 모집 안내, 문의 방법</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>• Đáp án đúng: cụm từ mô tả chính xác chủ đề/mục đích của poster</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>• Đáp án sai: cụm từ cùng format nhưng sai mục đích</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>• 4 đáp án PHẢI cùng dạng cấu trúc (đều là "danh từ + danh từ" hoặc "danh từ + 안내/방법/정보")</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>Quy tắc bắt buộc</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="10" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>1. Đáp án là cụm danh từ (~4-5 âm tiết) — KHÔNG phải từ đơn (từ đơn là 220003_a_1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>2. 4 đáp án PHẢI cùng cấu trúc: đều là "X 안내", hoặc đều là "X 보호/정보/방법/계획"</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>3. Poster phải có mục đích rõ ràng nhưng cần suy luận (không ghi trắng ra chủ đề)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>4. q_text PHẢI rỗng ""</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>5. q_image_description mô tả poster đủ để nhận ra mục đích</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="9" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
-      <c r="E58" s="10" t="n"/>
-      <c r="F58" s="10" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="B68" s="10" t="n"/>
+      <c r="C68" s="10" t="n"/>
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="10" t="n"/>
+      <c r="F68" s="10" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
         <is>
           <t>{</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "q_image_description": "포스터: 상단에 '시간을 알려 주는 친구' 텍스트, 중앙에 다양한 손목시계 이미지 3개, 하단에 '30% 할인 — 이번 주만!' 문구. 밝은 파란색 배경.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  "q_image_description": {</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "image": "포스터: 상단에 '깨끗한 지구를 위해' 제목, 중앙에 나무와 재활용 마크 그림, 하단에 '분리수거를 실천합시다', '일회용품 사용을 줄입시다' 문구. 초록색 배경."</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  },</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  "content": [{</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    "q_text": "",</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "q_answer": ["시계", "달력", "전화기", "가방"],</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="12" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "q_answer": ["환경 보호", "공원 소개", "날씨 정보", "여행 계획"],</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    "q_correct": 1</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  }]</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="12" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
         <is>
           <t>}</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t>• ① 시계 ✅ (đúng — 손목시계 이미지와 "시간을 알려 주는 친구")</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t>• ② 달력 (trap_similar_word — 시간 관련 물건이지만 시계가 아님)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t>• ③ 전화기 (trap_similar_word — 전자기기 category)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t>• ④ 가방 (trap_shared_noun — 착용하는 물건이지만 무관)</t>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>• ① 환경 보호 ✅ (재활용, 분리수거, 일회용품 줄이기 → 환경 보호)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>• ② 공원 소개 (trap_shared_noun — 나무 그림 있지만 공원이 아님)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>• ③ 날씨 정보 (trap_similar_word — 자연 관련이지만 날씨가 아님)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>• ④ 여행 계획 (trap_similar_word — 활동 관련이지만 여행이 아님)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="A41:F41"/>
+  <mergeCells count="49">
     <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A46:F46"/>
     <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A74:F74"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A50:F50"/>
     <mergeCell ref="A56:F56"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A62:F62"/>
     <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A72:F72"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A81:F81"/>
     <mergeCell ref="A63:F63"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A83:F83"/>
     <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A77:F77"/>
     <mergeCell ref="A64:F64"/>
     <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A73:F73"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A82:F82"/>
     <mergeCell ref="A60:F60"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A70:F70"/>
     <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A78:F78"/>
     <mergeCell ref="A69:F69"/>
     <mergeCell ref="A65:F65"/>
   </mergeCells>
